--- a/base_mundial_2026.xlsx
+++ b/base_mundial_2026.xlsx
@@ -1,30 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2. Proyectos Python\Mundial\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF37C778-FAC2-4A88-AF90-80A9599F6306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja2!$A$1:$J$673</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3518" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3998" uniqueCount="209">
   <si>
     <t>#</t>
   </si>
@@ -656,11 +647,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -698,21 +689,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -750,7 +733,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -784,7 +767,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -819,10 +801,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -995,11 +976,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1013,7 +994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1027,7 +1008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1041,7 +1022,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1055,7 +1036,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1069,7 +1050,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1083,7 +1064,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1097,7 +1078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1111,7 +1092,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1125,7 +1106,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1139,7 +1120,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1153,7 +1134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1167,7 +1148,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1181,7 +1162,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1195,7 +1176,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1209,7 +1190,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1223,7 +1204,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1237,7 +1218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1251,7 +1232,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1265,7 +1246,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1279,7 +1260,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1293,7 +1274,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1307,7 +1288,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1321,7 +1302,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1335,7 +1316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1349,7 +1330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1363,7 +1344,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1377,7 +1358,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1391,7 +1372,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1405,7 +1386,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1419,7 +1400,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1433,7 +1414,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1447,7 +1428,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1461,7 +1442,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1475,7 +1456,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1489,7 +1470,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1503,7 +1484,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1517,7 +1498,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1531,7 +1512,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1545,7 +1526,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1559,7 +1540,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1573,7 +1554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1587,7 +1568,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1601,7 +1582,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1615,7 +1596,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1629,7 +1610,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1643,7 +1624,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1657,7 +1638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1671,7 +1652,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1691,14 +1672,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J673"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J769"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>71</v>
       </c>
@@ -1730,7 +1708,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1740,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1794,7 +1772,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1826,7 +1804,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1858,7 +1836,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1890,7 +1868,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1922,7 +1900,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1954,7 +1932,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1986,7 +1964,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2018,7 +1996,7 @@
         <v>45805</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2050,7 +2028,7 @@
         <v>45739</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -2082,7 +2060,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2114,7 +2092,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2146,7 +2124,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2178,7 +2156,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -2210,7 +2188,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -2242,7 +2220,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -2274,7 +2252,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -2306,7 +2284,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -2338,7 +2316,7 @@
         <v>45937</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -2370,7 +2348,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -2402,7 +2380,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2434,7 +2412,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -2466,7 +2444,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -2498,7 +2476,7 @@
         <v>45580</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -2530,7 +2508,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2562,7 +2540,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -2594,7 +2572,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -2626,7 +2604,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -2658,7 +2636,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2690,7 +2668,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -2722,7 +2700,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -2754,7 +2732,7 @@
         <v>45904</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2786,7 +2764,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2818,7 +2796,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2850,7 +2828,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2882,7 +2860,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -2914,7 +2892,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -2946,7 +2924,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -2978,7 +2956,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -3010,7 +2988,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -3042,7 +3020,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -3074,7 +3052,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -3106,7 +3084,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -3138,7 +3116,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -3170,7 +3148,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -3202,7 +3180,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -3234,7 +3212,7 @@
         <v>45612</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -3266,7 +3244,7 @@
         <v>45579</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -3298,7 +3276,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -3330,7 +3308,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -3362,7 +3340,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -3394,7 +3372,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -3426,7 +3404,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -3458,7 +3436,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -3490,7 +3468,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -3522,7 +3500,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -3554,7 +3532,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -3586,7 +3564,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -3618,7 +3596,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -3650,7 +3628,7 @@
         <v>45580</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>81</v>
       </c>
@@ -3682,7 +3660,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>81</v>
       </c>
@@ -3714,7 +3692,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>81</v>
       </c>
@@ -3746,7 +3724,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>81</v>
       </c>
@@ -3778,7 +3756,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>81</v>
       </c>
@@ -3810,7 +3788,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -3842,7 +3820,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -3874,7 +3852,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -3906,7 +3884,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -3938,7 +3916,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -3970,7 +3948,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -4002,7 +3980,7 @@
         <v>45612</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -4034,7 +4012,7 @@
         <v>45579</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>34</v>
       </c>
@@ -4066,7 +4044,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
         <v>34</v>
       </c>
@@ -4098,7 +4076,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>34</v>
       </c>
@@ -4130,7 +4108,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -4162,7 +4140,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
         <v>34</v>
       </c>
@@ -4194,7 +4172,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -4226,7 +4204,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
         <v>34</v>
       </c>
@@ -4258,7 +4236,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>34</v>
       </c>
@@ -4290,7 +4268,7 @@
         <v>45904</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>34</v>
       </c>
@@ -4322,7 +4300,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -4354,7 +4332,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -4386,7 +4364,7 @@
         <v>45615</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -4418,7 +4396,7 @@
         <v>45580</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
         <v>30</v>
       </c>
@@ -4450,7 +4428,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -4482,7 +4460,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
         <v>30</v>
       </c>
@@ -4514,7 +4492,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -4546,7 +4524,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -4578,7 +4556,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -4610,7 +4588,7 @@
         <v>45943</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -4642,7 +4620,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -4674,7 +4652,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -4706,7 +4684,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -4738,7 +4716,7 @@
         <v>45580</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -4770,7 +4748,7 @@
         <v>45577</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -4802,7 +4780,7 @@
         <v>45543</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -4834,7 +4812,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -4866,7 +4844,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -4898,7 +4876,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -4930,7 +4908,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -4962,7 +4940,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -4994,7 +4972,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -5026,7 +5004,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -5058,7 +5036,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -5090,7 +5068,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -5122,7 +5100,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -5154,7 +5132,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -5186,7 +5164,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10">
       <c r="A110" t="s">
         <v>46</v>
       </c>
@@ -5218,7 +5196,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10">
       <c r="A111" t="s">
         <v>46</v>
       </c>
@@ -5250,7 +5228,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10">
       <c r="A112" t="s">
         <v>46</v>
       </c>
@@ -5282,7 +5260,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>46</v>
       </c>
@@ -5314,7 +5292,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>46</v>
       </c>
@@ -5346,7 +5324,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>46</v>
       </c>
@@ -5378,7 +5356,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>46</v>
       </c>
@@ -5410,7 +5388,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>46</v>
       </c>
@@ -5442,7 +5420,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -5474,7 +5452,7 @@
         <v>45911</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
         <v>46</v>
       </c>
@@ -5506,7 +5484,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -5538,7 +5516,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
         <v>46</v>
       </c>
@@ -5570,7 +5548,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
         <v>28</v>
       </c>
@@ -5602,7 +5580,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
         <v>28</v>
       </c>
@@ -5634,7 +5612,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
         <v>28</v>
       </c>
@@ -5666,7 +5644,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
         <v>28</v>
       </c>
@@ -5698,7 +5676,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
         <v>28</v>
       </c>
@@ -5730,7 +5708,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
         <v>28</v>
       </c>
@@ -5762,7 +5740,7 @@
         <v>45948</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
         <v>28</v>
       </c>
@@ -5794,7 +5772,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10">
       <c r="A129" t="s">
         <v>28</v>
       </c>
@@ -5826,7 +5804,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10">
       <c r="A130" t="s">
         <v>28</v>
       </c>
@@ -5858,7 +5836,7 @@
         <v>45911</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10">
       <c r="A131" t="s">
         <v>28</v>
       </c>
@@ -5890,7 +5868,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10">
       <c r="A132" t="s">
         <v>28</v>
       </c>
@@ -5922,7 +5900,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10">
       <c r="A133" t="s">
         <v>28</v>
       </c>
@@ -5954,7 +5932,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -5986,7 +5964,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -6018,7 +5996,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10">
       <c r="A136" t="s">
         <v>8</v>
       </c>
@@ -6050,7 +6028,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -6082,7 +6060,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -6114,7 +6092,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -6146,7 +6124,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10">
       <c r="A140" t="s">
         <v>8</v>
       </c>
@@ -6178,7 +6156,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -6210,7 +6188,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -6242,7 +6220,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -6274,7 +6252,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -6306,7 +6284,7 @@
         <v>45739</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10">
       <c r="A145" t="s">
         <v>8</v>
       </c>
@@ -6338,7 +6316,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -6370,7 +6348,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -6402,7 +6380,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -6434,7 +6412,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -6466,7 +6444,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -6498,7 +6476,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -6530,7 +6508,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -6562,7 +6540,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -6594,7 +6572,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -6626,7 +6604,7 @@
         <v>45675</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -6658,7 +6636,7 @@
         <v>45669</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -6690,7 +6668,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -6722,7 +6700,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10">
       <c r="A158" t="s">
         <v>14</v>
       </c>
@@ -6754,7 +6732,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10">
       <c r="A159" t="s">
         <v>14</v>
       </c>
@@ -6786,7 +6764,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10">
       <c r="A160" t="s">
         <v>14</v>
       </c>
@@ -6818,7 +6796,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10">
       <c r="A161" t="s">
         <v>14</v>
       </c>
@@ -6850,7 +6828,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10">
       <c r="A162" t="s">
         <v>14</v>
       </c>
@@ -6882,7 +6860,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10">
       <c r="A163" t="s">
         <v>14</v>
       </c>
@@ -6914,7 +6892,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10">
       <c r="A164" t="s">
         <v>14</v>
       </c>
@@ -6946,7 +6924,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10">
       <c r="A165" t="s">
         <v>14</v>
       </c>
@@ -6978,7 +6956,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10">
       <c r="A166" t="s">
         <v>14</v>
       </c>
@@ -7010,7 +6988,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10">
       <c r="A167" t="s">
         <v>14</v>
       </c>
@@ -7042,7 +7020,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10">
       <c r="A168" t="s">
         <v>14</v>
       </c>
@@ -7074,7 +7052,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10">
       <c r="A169" t="s">
         <v>14</v>
       </c>
@@ -7106,7 +7084,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10">
       <c r="A170" t="s">
         <v>31</v>
       </c>
@@ -7138,7 +7116,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10">
       <c r="A171" t="s">
         <v>31</v>
       </c>
@@ -7170,7 +7148,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10">
       <c r="A172" t="s">
         <v>31</v>
       </c>
@@ -7202,7 +7180,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10">
       <c r="A173" t="s">
         <v>31</v>
       </c>
@@ -7234,7 +7212,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10">
       <c r="A174" t="s">
         <v>31</v>
       </c>
@@ -7266,7 +7244,7 @@
         <v>45977</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10">
       <c r="A175" t="s">
         <v>31</v>
       </c>
@@ -7298,7 +7276,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10">
       <c r="A176" t="s">
         <v>31</v>
       </c>
@@ -7330,7 +7308,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10">
       <c r="A177" t="s">
         <v>31</v>
       </c>
@@ -7362,7 +7340,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10">
       <c r="A178" t="s">
         <v>31</v>
       </c>
@@ -7394,7 +7372,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10">
       <c r="A179" t="s">
         <v>31</v>
       </c>
@@ -7426,7 +7404,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10">
       <c r="A180" t="s">
         <v>31</v>
       </c>
@@ -7458,7 +7436,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10">
       <c r="A181" t="s">
         <v>31</v>
       </c>
@@ -7490,7 +7468,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10">
       <c r="A182" t="s">
         <v>33</v>
       </c>
@@ -7522,7 +7500,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10">
       <c r="A183" t="s">
         <v>33</v>
       </c>
@@ -7554,7 +7532,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10">
       <c r="A184" t="s">
         <v>33</v>
       </c>
@@ -7586,7 +7564,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10">
       <c r="A185" t="s">
         <v>33</v>
       </c>
@@ -7618,7 +7596,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10">
       <c r="A186" t="s">
         <v>33</v>
       </c>
@@ -7650,7 +7628,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10">
       <c r="A187" t="s">
         <v>33</v>
       </c>
@@ -7682,7 +7660,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10">
       <c r="A188" t="s">
         <v>33</v>
       </c>
@@ -7714,7 +7692,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10">
       <c r="A189" t="s">
         <v>33</v>
       </c>
@@ -7746,7 +7724,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10">
       <c r="A190" t="s">
         <v>33</v>
       </c>
@@ -7778,7 +7756,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10">
       <c r="A191" t="s">
         <v>33</v>
       </c>
@@ -7810,7 +7788,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10">
       <c r="A192" t="s">
         <v>33</v>
       </c>
@@ -7842,7 +7820,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10">
       <c r="A193" t="s">
         <v>33</v>
       </c>
@@ -7874,7 +7852,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -7906,7 +7884,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -7938,7 +7916,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -7970,7 +7948,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -8002,7 +7980,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10">
       <c r="A198" t="s">
         <v>16</v>
       </c>
@@ -8034,7 +8012,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -8066,7 +8044,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -8098,7 +8076,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -8130,7 +8108,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -8162,7 +8140,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -8194,7 +8172,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -8226,7 +8204,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -8258,7 +8236,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -8290,7 +8268,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -8322,7 +8300,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -8354,7 +8332,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -8386,7 +8364,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -8418,7 +8396,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -8450,7 +8428,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -8482,7 +8460,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -8514,7 +8492,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -8546,7 +8524,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -8578,7 +8556,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -8610,7 +8588,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10">
       <c r="A217" t="s">
         <v>13</v>
       </c>
@@ -8642,7 +8620,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10">
       <c r="A218" t="s">
         <v>43</v>
       </c>
@@ -8674,7 +8652,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10">
       <c r="A219" t="s">
         <v>43</v>
       </c>
@@ -8706,7 +8684,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10">
       <c r="A220" t="s">
         <v>43</v>
       </c>
@@ -8738,7 +8716,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10">
       <c r="A221" t="s">
         <v>43</v>
       </c>
@@ -8770,7 +8748,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10">
       <c r="A222" t="s">
         <v>43</v>
       </c>
@@ -8802,7 +8780,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10">
       <c r="A223" t="s">
         <v>43</v>
       </c>
@@ -8834,7 +8812,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10">
       <c r="A224" t="s">
         <v>43</v>
       </c>
@@ -8866,7 +8844,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10">
       <c r="A225" t="s">
         <v>43</v>
       </c>
@@ -8898,7 +8876,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10">
       <c r="A226" t="s">
         <v>43</v>
       </c>
@@ -8930,7 +8908,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10">
       <c r="A227" t="s">
         <v>43</v>
       </c>
@@ -8962,7 +8940,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10">
       <c r="A228" t="s">
         <v>43</v>
       </c>
@@ -8994,7 +8972,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10">
       <c r="A229" t="s">
         <v>43</v>
       </c>
@@ -9026,7 +9004,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10">
       <c r="A230" t="s">
         <v>7</v>
       </c>
@@ -9058,7 +9036,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10">
       <c r="A231" t="s">
         <v>7</v>
       </c>
@@ -9090,7 +9068,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10">
       <c r="A232" t="s">
         <v>7</v>
       </c>
@@ -9122,7 +9100,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10">
       <c r="A233" t="s">
         <v>7</v>
       </c>
@@ -9154,7 +9132,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10">
       <c r="A234" t="s">
         <v>7</v>
       </c>
@@ -9186,7 +9164,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10">
       <c r="A235" t="s">
         <v>7</v>
       </c>
@@ -9218,7 +9196,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10">
       <c r="A236" t="s">
         <v>7</v>
       </c>
@@ -9250,7 +9228,7 @@
         <v>45943</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10">
       <c r="A237" t="s">
         <v>7</v>
       </c>
@@ -9282,7 +9260,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10">
       <c r="A238" t="s">
         <v>7</v>
       </c>
@@ -9314,7 +9292,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10">
       <c r="A239" t="s">
         <v>7</v>
       </c>
@@ -9346,7 +9324,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10">
       <c r="A240" t="s">
         <v>7</v>
       </c>
@@ -9378,7 +9356,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10">
       <c r="A241" t="s">
         <v>7</v>
       </c>
@@ -9410,7 +9388,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10">
       <c r="A242" t="s">
         <v>25</v>
       </c>
@@ -9442,7 +9420,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10">
       <c r="A243" t="s">
         <v>25</v>
       </c>
@@ -9474,7 +9452,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10">
       <c r="A244" t="s">
         <v>25</v>
       </c>
@@ -9506,7 +9484,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10">
       <c r="A245" t="s">
         <v>25</v>
       </c>
@@ -9538,7 +9516,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10">
       <c r="A246" t="s">
         <v>25</v>
       </c>
@@ -9570,7 +9548,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10">
       <c r="A247" t="s">
         <v>25</v>
       </c>
@@ -9602,7 +9580,7 @@
         <v>45943</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10">
       <c r="A248" t="s">
         <v>25</v>
       </c>
@@ -9634,7 +9612,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10">
       <c r="A249" t="s">
         <v>25</v>
       </c>
@@ -9666,7 +9644,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10">
       <c r="A250" t="s">
         <v>25</v>
       </c>
@@ -9698,7 +9676,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10">
       <c r="A251" t="s">
         <v>25</v>
       </c>
@@ -9730,7 +9708,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10">
       <c r="A252" t="s">
         <v>25</v>
       </c>
@@ -9762,7 +9740,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10">
       <c r="A253" t="s">
         <v>25</v>
       </c>
@@ -9794,7 +9772,7 @@
         <v>45686</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10">
       <c r="A254" t="s">
         <v>29</v>
       </c>
@@ -9826,7 +9804,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10">
       <c r="A255" t="s">
         <v>29</v>
       </c>
@@ -9858,7 +9836,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10">
       <c r="A256" t="s">
         <v>29</v>
       </c>
@@ -9890,7 +9868,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10">
       <c r="A257" t="s">
         <v>29</v>
       </c>
@@ -9922,7 +9900,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10">
       <c r="A258" t="s">
         <v>29</v>
       </c>
@@ -9954,7 +9932,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10">
       <c r="A259" t="s">
         <v>29</v>
       </c>
@@ -9986,7 +9964,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10">
       <c r="A260" t="s">
         <v>29</v>
       </c>
@@ -10018,7 +9996,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10">
       <c r="A261" t="s">
         <v>29</v>
       </c>
@@ -10050,7 +10028,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10">
       <c r="A262" t="s">
         <v>29</v>
       </c>
@@ -10082,7 +10060,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10">
       <c r="A263" t="s">
         <v>29</v>
       </c>
@@ -10114,7 +10092,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10">
       <c r="A264" t="s">
         <v>29</v>
       </c>
@@ -10146,7 +10124,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10">
       <c r="A265" t="s">
         <v>29</v>
       </c>
@@ -10178,7 +10156,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10">
       <c r="A266" t="s">
         <v>38</v>
       </c>
@@ -10210,7 +10188,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10">
       <c r="A267" t="s">
         <v>38</v>
       </c>
@@ -10242,7 +10220,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10">
       <c r="A268" t="s">
         <v>38</v>
       </c>
@@ -10274,7 +10252,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10">
       <c r="A269" t="s">
         <v>38</v>
       </c>
@@ -10306,7 +10284,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10">
       <c r="A270" t="s">
         <v>38</v>
       </c>
@@ -10338,7 +10316,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10">
       <c r="A271" t="s">
         <v>38</v>
       </c>
@@ -10370,7 +10348,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10">
       <c r="A272" t="s">
         <v>38</v>
       </c>
@@ -10402,7 +10380,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10">
       <c r="A273" t="s">
         <v>38</v>
       </c>
@@ -10434,7 +10412,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10">
       <c r="A274" t="s">
         <v>38</v>
       </c>
@@ -10466,7 +10444,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10">
       <c r="A275" t="s">
         <v>38</v>
       </c>
@@ -10498,7 +10476,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10">
       <c r="A276" t="s">
         <v>38</v>
       </c>
@@ -10530,7 +10508,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10">
       <c r="A277" t="s">
         <v>38</v>
       </c>
@@ -10562,7 +10540,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10">
       <c r="A278" t="s">
         <v>50</v>
       </c>
@@ -10594,7 +10572,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10">
       <c r="A279" t="s">
         <v>50</v>
       </c>
@@ -10626,7 +10604,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10">
       <c r="A280" t="s">
         <v>50</v>
       </c>
@@ -10658,7 +10636,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10">
       <c r="A281" t="s">
         <v>50</v>
       </c>
@@ -10690,7 +10668,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10">
       <c r="A282" t="s">
         <v>50</v>
       </c>
@@ -10722,7 +10700,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10">
       <c r="A283" t="s">
         <v>50</v>
       </c>
@@ -10754,7 +10732,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10">
       <c r="A284" t="s">
         <v>50</v>
       </c>
@@ -10786,7 +10764,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10">
       <c r="A285" t="s">
         <v>50</v>
       </c>
@@ -10818,7 +10796,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10">
       <c r="A286" t="s">
         <v>50</v>
       </c>
@@ -10850,7 +10828,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10">
       <c r="A287" t="s">
         <v>50</v>
       </c>
@@ -10882,7 +10860,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10">
       <c r="A288" t="s">
         <v>50</v>
       </c>
@@ -10914,7 +10892,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10">
       <c r="A289" t="s">
         <v>50</v>
       </c>
@@ -10946,7 +10924,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -10978,7 +10956,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -11010,7 +10988,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -11042,7 +11020,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -11074,7 +11052,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -11106,7 +11084,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -11138,7 +11116,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -11170,7 +11148,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -11202,7 +11180,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -11234,7 +11212,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -11266,7 +11244,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -11298,7 +11276,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -11330,7 +11308,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10">
       <c r="A302" t="s">
         <v>37</v>
       </c>
@@ -11362,7 +11340,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10">
       <c r="A303" t="s">
         <v>37</v>
       </c>
@@ -11394,7 +11372,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10">
       <c r="A304" t="s">
         <v>37</v>
       </c>
@@ -11426,7 +11404,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10">
       <c r="A305" t="s">
         <v>37</v>
       </c>
@@ -11458,7 +11436,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10">
       <c r="A306" t="s">
         <v>37</v>
       </c>
@@ -11490,7 +11468,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10">
       <c r="A307" t="s">
         <v>37</v>
       </c>
@@ -11522,7 +11500,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10">
       <c r="A308" t="s">
         <v>37</v>
       </c>
@@ -11554,7 +11532,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10">
       <c r="A309" t="s">
         <v>37</v>
       </c>
@@ -11586,7 +11564,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10">
       <c r="A310" t="s">
         <v>37</v>
       </c>
@@ -11618,7 +11596,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10">
       <c r="A311" t="s">
         <v>37</v>
       </c>
@@ -11650,7 +11628,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10">
       <c r="A312" t="s">
         <v>37</v>
       </c>
@@ -11682,7 +11660,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10">
       <c r="A313" t="s">
         <v>37</v>
       </c>
@@ -11714,7 +11692,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10">
       <c r="A314" t="s">
         <v>44</v>
       </c>
@@ -11746,7 +11724,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10">
       <c r="A315" t="s">
         <v>44</v>
       </c>
@@ -11778,7 +11756,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10">
       <c r="A316" t="s">
         <v>44</v>
       </c>
@@ -11810,7 +11788,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10">
       <c r="A317" t="s">
         <v>44</v>
       </c>
@@ -11842,7 +11820,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10">
       <c r="A318" t="s">
         <v>44</v>
       </c>
@@ -11874,7 +11852,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10">
       <c r="A319" t="s">
         <v>44</v>
       </c>
@@ -11906,7 +11884,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10">
       <c r="A320" t="s">
         <v>44</v>
       </c>
@@ -11938,7 +11916,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10">
       <c r="A321" t="s">
         <v>44</v>
       </c>
@@ -11970,7 +11948,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10">
       <c r="A322" t="s">
         <v>44</v>
       </c>
@@ -12002,7 +11980,7 @@
         <v>45906</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10">
       <c r="A323" t="s">
         <v>44</v>
       </c>
@@ -12034,7 +12012,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10">
       <c r="A324" t="s">
         <v>44</v>
       </c>
@@ -12066,7 +12044,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10">
       <c r="A325" t="s">
         <v>44</v>
       </c>
@@ -12098,7 +12076,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10">
       <c r="A326" t="s">
         <v>51</v>
       </c>
@@ -12130,7 +12108,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10">
       <c r="A327" t="s">
         <v>51</v>
       </c>
@@ -12162,7 +12140,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10">
       <c r="A328" t="s">
         <v>51</v>
       </c>
@@ -12194,7 +12172,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10">
       <c r="A329" t="s">
         <v>51</v>
       </c>
@@ -12226,7 +12204,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10">
       <c r="A330" t="s">
         <v>51</v>
       </c>
@@ -12258,7 +12236,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10">
       <c r="A331" t="s">
         <v>51</v>
       </c>
@@ -12290,7 +12268,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10">
       <c r="A332" t="s">
         <v>51</v>
       </c>
@@ -12322,7 +12300,7 @@
         <v>45906</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10">
       <c r="A333" t="s">
         <v>51</v>
       </c>
@@ -12354,7 +12332,7 @@
         <v>45902</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10">
       <c r="A334" t="s">
         <v>51</v>
       </c>
@@ -12386,7 +12364,7 @@
         <v>45820</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10">
       <c r="A335" t="s">
         <v>51</v>
       </c>
@@ -12418,7 +12396,7 @@
         <v>45815</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10">
       <c r="A336" t="s">
         <v>51</v>
       </c>
@@ -12450,7 +12428,7 @@
         <v>45743</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10">
       <c r="A337" t="s">
         <v>51</v>
       </c>
@@ -12482,7 +12460,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10">
       <c r="A338" t="s">
         <v>21</v>
       </c>
@@ -12514,7 +12492,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10">
       <c r="A339" t="s">
         <v>21</v>
       </c>
@@ -12546,7 +12524,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10">
       <c r="A340" t="s">
         <v>21</v>
       </c>
@@ -12578,7 +12556,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10">
       <c r="A341" t="s">
         <v>21</v>
       </c>
@@ -12610,7 +12588,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10">
       <c r="A342" t="s">
         <v>21</v>
       </c>
@@ -12642,7 +12620,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10">
       <c r="A343" t="s">
         <v>21</v>
       </c>
@@ -12674,7 +12652,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10">
       <c r="A344" t="s">
         <v>21</v>
       </c>
@@ -12706,7 +12684,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10">
       <c r="A345" t="s">
         <v>21</v>
       </c>
@@ -12738,7 +12716,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10">
       <c r="A346" t="s">
         <v>21</v>
       </c>
@@ -12770,7 +12748,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10">
       <c r="A347" t="s">
         <v>21</v>
       </c>
@@ -12802,7 +12780,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10">
       <c r="A348" t="s">
         <v>21</v>
       </c>
@@ -12834,7 +12812,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10">
       <c r="A349" t="s">
         <v>21</v>
       </c>
@@ -12866,7 +12844,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10">
       <c r="A350" t="s">
         <v>15</v>
       </c>
@@ -12898,7 +12876,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10">
       <c r="A351" t="s">
         <v>15</v>
       </c>
@@ -12930,7 +12908,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10">
       <c r="A352" t="s">
         <v>15</v>
       </c>
@@ -12962,7 +12940,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10">
       <c r="A353" t="s">
         <v>15</v>
       </c>
@@ -12994,7 +12972,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10">
       <c r="A354" t="s">
         <v>15</v>
       </c>
@@ -13026,7 +13004,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10">
       <c r="A355" t="s">
         <v>15</v>
       </c>
@@ -13058,7 +13036,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10">
       <c r="A356" t="s">
         <v>15</v>
       </c>
@@ -13090,7 +13068,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10">
       <c r="A357" t="s">
         <v>15</v>
       </c>
@@ -13122,7 +13100,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10">
       <c r="A358" t="s">
         <v>15</v>
       </c>
@@ -13154,7 +13132,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10">
       <c r="A359" t="s">
         <v>15</v>
       </c>
@@ -13186,7 +13164,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10">
       <c r="A360" t="s">
         <v>15</v>
       </c>
@@ -13218,7 +13196,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10">
       <c r="A361" t="s">
         <v>15</v>
       </c>
@@ -13250,7 +13228,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10">
       <c r="A362" t="s">
         <v>42</v>
       </c>
@@ -13282,7 +13260,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10">
       <c r="A363" t="s">
         <v>42</v>
       </c>
@@ -13314,7 +13292,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10">
       <c r="A364" t="s">
         <v>42</v>
       </c>
@@ -13346,7 +13324,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10">
       <c r="A365" t="s">
         <v>42</v>
       </c>
@@ -13378,7 +13356,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10">
       <c r="A366" t="s">
         <v>42</v>
       </c>
@@ -13410,7 +13388,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10">
       <c r="A367" t="s">
         <v>42</v>
       </c>
@@ -13442,7 +13420,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10">
       <c r="A368" t="s">
         <v>42</v>
       </c>
@@ -13474,7 +13452,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10">
       <c r="A369" t="s">
         <v>42</v>
       </c>
@@ -13506,7 +13484,7 @@
         <v>45906</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10">
       <c r="A370" t="s">
         <v>42</v>
       </c>
@@ -13538,7 +13516,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10">
       <c r="A371" t="s">
         <v>42</v>
       </c>
@@ -13570,7 +13548,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10">
       <c r="A372" t="s">
         <v>42</v>
       </c>
@@ -13602,7 +13580,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10">
       <c r="A373" t="s">
         <v>42</v>
       </c>
@@ -13634,7 +13612,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10">
       <c r="A374" t="s">
         <v>32</v>
       </c>
@@ -13666,7 +13644,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10">
       <c r="A375" t="s">
         <v>32</v>
       </c>
@@ -13698,7 +13676,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10">
       <c r="A376" t="s">
         <v>32</v>
       </c>
@@ -13730,7 +13708,7 @@
         <v>45739</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10">
       <c r="A377" t="s">
         <v>32</v>
       </c>
@@ -13762,7 +13740,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10">
       <c r="A378" t="s">
         <v>32</v>
       </c>
@@ -13794,7 +13772,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10">
       <c r="A379" t="s">
         <v>32</v>
       </c>
@@ -13826,7 +13804,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10">
       <c r="A380" t="s">
         <v>32</v>
       </c>
@@ -13858,7 +13836,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10">
       <c r="A381" t="s">
         <v>32</v>
       </c>
@@ -13890,7 +13868,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10">
       <c r="A382" t="s">
         <v>32</v>
       </c>
@@ -13922,7 +13900,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10">
       <c r="A383" t="s">
         <v>32</v>
       </c>
@@ -13954,7 +13932,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10">
       <c r="A384" t="s">
         <v>32</v>
       </c>
@@ -13986,7 +13964,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10">
       <c r="A385" t="s">
         <v>32</v>
       </c>
@@ -14018,7 +13996,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10">
       <c r="A386" t="s">
         <v>22</v>
       </c>
@@ -14050,7 +14028,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10">
       <c r="A387" t="s">
         <v>22</v>
       </c>
@@ -14082,7 +14060,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10">
       <c r="A388" t="s">
         <v>22</v>
       </c>
@@ -14114,7 +14092,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10">
       <c r="A389" t="s">
         <v>22</v>
       </c>
@@ -14146,7 +14124,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10">
       <c r="A390" t="s">
         <v>22</v>
       </c>
@@ -14178,7 +14156,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10">
       <c r="A391" t="s">
         <v>22</v>
       </c>
@@ -14210,7 +14188,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10">
       <c r="A392" t="s">
         <v>22</v>
       </c>
@@ -14242,7 +14220,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10">
       <c r="A393" t="s">
         <v>22</v>
       </c>
@@ -14274,7 +14252,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10">
       <c r="A394" t="s">
         <v>22</v>
       </c>
@@ -14306,7 +14284,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10">
       <c r="A395" t="s">
         <v>22</v>
       </c>
@@ -14338,7 +14316,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10">
       <c r="A396" t="s">
         <v>22</v>
       </c>
@@ -14370,7 +14348,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10">
       <c r="A397" t="s">
         <v>22</v>
       </c>
@@ -14402,7 +14380,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10">
       <c r="A398" t="s">
         <v>48</v>
       </c>
@@ -14434,7 +14412,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10">
       <c r="A399" t="s">
         <v>48</v>
       </c>
@@ -14466,7 +14444,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10">
       <c r="A400" t="s">
         <v>48</v>
       </c>
@@ -14498,7 +14476,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10">
       <c r="A401" t="s">
         <v>48</v>
       </c>
@@ -14530,7 +14508,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10">
       <c r="A402" t="s">
         <v>48</v>
       </c>
@@ -14562,7 +14540,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10">
       <c r="A403" t="s">
         <v>48</v>
       </c>
@@ -14594,7 +14572,7 @@
         <v>45943</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10">
       <c r="A404" t="s">
         <v>48</v>
       </c>
@@ -14626,7 +14604,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10">
       <c r="A405" t="s">
         <v>48</v>
       </c>
@@ -14658,7 +14636,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10">
       <c r="A406" t="s">
         <v>48</v>
       </c>
@@ -14690,7 +14668,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10">
       <c r="A407" t="s">
         <v>48</v>
       </c>
@@ -14722,7 +14700,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10">
       <c r="A408" t="s">
         <v>48</v>
       </c>
@@ -14754,7 +14732,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10">
       <c r="A409" t="s">
         <v>48</v>
       </c>
@@ -14786,7 +14764,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10">
       <c r="A410" t="s">
         <v>36</v>
       </c>
@@ -14818,7 +14796,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10">
       <c r="A411" t="s">
         <v>36</v>
       </c>
@@ -14850,7 +14828,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10">
       <c r="A412" t="s">
         <v>36</v>
       </c>
@@ -14882,7 +14860,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10">
       <c r="A413" t="s">
         <v>36</v>
       </c>
@@ -14914,7 +14892,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10">
       <c r="A414" t="s">
         <v>36</v>
       </c>
@@ -14946,7 +14924,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10">
       <c r="A415" t="s">
         <v>36</v>
       </c>
@@ -14978,7 +14956,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10">
       <c r="A416" t="s">
         <v>36</v>
       </c>
@@ -15010,7 +14988,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10">
       <c r="A417" t="s">
         <v>36</v>
       </c>
@@ -15042,7 +15020,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10">
       <c r="A418" t="s">
         <v>36</v>
       </c>
@@ -15074,7 +15052,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10">
       <c r="A419" t="s">
         <v>36</v>
       </c>
@@ -15106,7 +15084,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10">
       <c r="A420" t="s">
         <v>36</v>
       </c>
@@ -15138,7 +15116,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10">
       <c r="A421" t="s">
         <v>36</v>
       </c>
@@ -15170,7 +15148,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10">
       <c r="A422" t="s">
         <v>24</v>
       </c>
@@ -15202,7 +15180,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10">
       <c r="A423" t="s">
         <v>24</v>
       </c>
@@ -15234,7 +15212,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10">
       <c r="A424" t="s">
         <v>24</v>
       </c>
@@ -15266,7 +15244,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10">
       <c r="A425" t="s">
         <v>24</v>
       </c>
@@ -15298,7 +15276,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10">
       <c r="A426" t="s">
         <v>24</v>
       </c>
@@ -15330,7 +15308,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10">
       <c r="A427" t="s">
         <v>24</v>
       </c>
@@ -15362,7 +15340,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10">
       <c r="A428" t="s">
         <v>24</v>
       </c>
@@ -15394,7 +15372,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10">
       <c r="A429" t="s">
         <v>24</v>
       </c>
@@ -15426,7 +15404,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10">
       <c r="A430" t="s">
         <v>24</v>
       </c>
@@ -15458,7 +15436,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10">
       <c r="A431" t="s">
         <v>24</v>
       </c>
@@ -15490,7 +15468,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10">
       <c r="A432" t="s">
         <v>24</v>
       </c>
@@ -15522,7 +15500,7 @@
         <v>45613</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10">
       <c r="A433" t="s">
         <v>24</v>
       </c>
@@ -15554,7 +15532,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10">
       <c r="A434" t="s">
         <v>10</v>
       </c>
@@ -15586,7 +15564,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10">
       <c r="A435" t="s">
         <v>10</v>
       </c>
@@ -15618,7 +15596,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10">
       <c r="A436" t="s">
         <v>10</v>
       </c>
@@ -15650,7 +15628,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10">
       <c r="A437" t="s">
         <v>10</v>
       </c>
@@ -15682,7 +15660,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10">
       <c r="A438" t="s">
         <v>10</v>
       </c>
@@ -15714,7 +15692,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10">
       <c r="A439" t="s">
         <v>10</v>
       </c>
@@ -15746,7 +15724,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10">
       <c r="A440" t="s">
         <v>10</v>
       </c>
@@ -15778,7 +15756,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10">
       <c r="A441" t="s">
         <v>10</v>
       </c>
@@ -15810,7 +15788,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10">
       <c r="A442" t="s">
         <v>10</v>
       </c>
@@ -15842,7 +15820,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10">
       <c r="A443" t="s">
         <v>10</v>
       </c>
@@ -15874,7 +15852,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10">
       <c r="A444" t="s">
         <v>10</v>
       </c>
@@ -15906,7 +15884,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10">
       <c r="A445" t="s">
         <v>10</v>
       </c>
@@ -15938,7 +15916,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10">
       <c r="A446" t="s">
         <v>41</v>
       </c>
@@ -15970,7 +15948,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10">
       <c r="A447" t="s">
         <v>41</v>
       </c>
@@ -16002,7 +15980,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10">
       <c r="A448" t="s">
         <v>41</v>
       </c>
@@ -16034,7 +16012,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10">
       <c r="A449" t="s">
         <v>41</v>
       </c>
@@ -16066,7 +16044,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10">
       <c r="A450" t="s">
         <v>41</v>
       </c>
@@ -16098,7 +16076,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10">
       <c r="A451" t="s">
         <v>41</v>
       </c>
@@ -16130,7 +16108,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10">
       <c r="A452" t="s">
         <v>41</v>
       </c>
@@ -16162,7 +16140,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10">
       <c r="A453" t="s">
         <v>41</v>
       </c>
@@ -16194,7 +16172,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10">
       <c r="A454" t="s">
         <v>41</v>
       </c>
@@ -16226,7 +16204,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10">
       <c r="A455" t="s">
         <v>41</v>
       </c>
@@ -16258,7 +16236,7 @@
         <v>45906</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10">
       <c r="A456" t="s">
         <v>41</v>
       </c>
@@ -16290,7 +16268,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10">
       <c r="A457" t="s">
         <v>41</v>
       </c>
@@ -16322,7 +16300,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10">
       <c r="A458" t="s">
         <v>17</v>
       </c>
@@ -16354,7 +16332,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10">
       <c r="A459" t="s">
         <v>17</v>
       </c>
@@ -16386,7 +16364,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10">
       <c r="A460" t="s">
         <v>17</v>
       </c>
@@ -16418,7 +16396,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10">
       <c r="A461" t="s">
         <v>17</v>
       </c>
@@ -16450,7 +16428,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10">
       <c r="A462" t="s">
         <v>17</v>
       </c>
@@ -16482,7 +16460,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10">
       <c r="A463" t="s">
         <v>17</v>
       </c>
@@ -16514,7 +16492,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10">
       <c r="A464" t="s">
         <v>17</v>
       </c>
@@ -16546,7 +16524,7 @@
         <v>45910</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10">
       <c r="A465" t="s">
         <v>17</v>
       </c>
@@ -16578,7 +16556,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10">
       <c r="A466" t="s">
         <v>17</v>
       </c>
@@ -16610,7 +16588,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10">
       <c r="A467" t="s">
         <v>17</v>
       </c>
@@ -16642,7 +16620,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10">
       <c r="A468" t="s">
         <v>17</v>
       </c>
@@ -16674,7 +16652,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10">
       <c r="A469" t="s">
         <v>17</v>
       </c>
@@ -16706,7 +16684,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10">
       <c r="A470" t="s">
         <v>39</v>
       </c>
@@ -16738,7 +16716,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10">
       <c r="A471" t="s">
         <v>39</v>
       </c>
@@ -16770,7 +16748,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10">
       <c r="A472" t="s">
         <v>39</v>
       </c>
@@ -16802,7 +16780,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10">
       <c r="A473" t="s">
         <v>39</v>
       </c>
@@ -16834,7 +16812,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10">
       <c r="A474" t="s">
         <v>39</v>
       </c>
@@ -16866,7 +16844,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10">
       <c r="A475" t="s">
         <v>39</v>
       </c>
@@ -16898,7 +16876,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10">
       <c r="A476" t="s">
         <v>39</v>
       </c>
@@ -16930,7 +16908,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10">
       <c r="A477" t="s">
         <v>39</v>
       </c>
@@ -16962,7 +16940,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10">
       <c r="A478" t="s">
         <v>39</v>
       </c>
@@ -16994,7 +16972,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10">
       <c r="A479" t="s">
         <v>39</v>
       </c>
@@ -17026,7 +17004,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10">
       <c r="A480" t="s">
         <v>39</v>
       </c>
@@ -17058,7 +17036,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10">
       <c r="A481" t="s">
         <v>39</v>
       </c>
@@ -17090,7 +17068,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10">
       <c r="A482" t="s">
         <v>26</v>
       </c>
@@ -17122,7 +17100,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10">
       <c r="A483" t="s">
         <v>26</v>
       </c>
@@ -17154,7 +17132,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10">
       <c r="A484" t="s">
         <v>26</v>
       </c>
@@ -17186,7 +17164,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10">
       <c r="A485" t="s">
         <v>26</v>
       </c>
@@ -17218,7 +17196,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10">
       <c r="A486" t="s">
         <v>26</v>
       </c>
@@ -17250,7 +17228,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10">
       <c r="A487" t="s">
         <v>26</v>
       </c>
@@ -17282,7 +17260,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10">
       <c r="A488" t="s">
         <v>26</v>
       </c>
@@ -17314,7 +17292,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:10">
       <c r="A489" t="s">
         <v>26</v>
       </c>
@@ -17346,7 +17324,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:10">
       <c r="A490" t="s">
         <v>26</v>
       </c>
@@ -17378,7 +17356,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:10">
       <c r="A491" t="s">
         <v>26</v>
       </c>
@@ -17410,7 +17388,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:10">
       <c r="A492" t="s">
         <v>26</v>
       </c>
@@ -17442,7 +17420,7 @@
         <v>45911</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:10">
       <c r="A493" t="s">
         <v>26</v>
       </c>
@@ -17474,7 +17452,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:10">
       <c r="A494" t="s">
         <v>12</v>
       </c>
@@ -17506,7 +17484,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:10">
       <c r="A495" t="s">
         <v>12</v>
       </c>
@@ -17538,7 +17516,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:10">
       <c r="A496" t="s">
         <v>12</v>
       </c>
@@ -17570,7 +17548,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:10">
       <c r="A497" t="s">
         <v>12</v>
       </c>
@@ -17602,7 +17580,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:10">
       <c r="A498" t="s">
         <v>12</v>
       </c>
@@ -17634,7 +17612,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:10">
       <c r="A499" t="s">
         <v>12</v>
       </c>
@@ -17666,7 +17644,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:10">
       <c r="A500" t="s">
         <v>12</v>
       </c>
@@ -17698,7 +17676,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:10">
       <c r="A501" t="s">
         <v>12</v>
       </c>
@@ -17730,7 +17708,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:10">
       <c r="A502" t="s">
         <v>12</v>
       </c>
@@ -17762,7 +17740,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:10">
       <c r="A503" t="s">
         <v>12</v>
       </c>
@@ -17794,7 +17772,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:10">
       <c r="A504" t="s">
         <v>12</v>
       </c>
@@ -17826,7 +17804,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:10">
       <c r="A505" t="s">
         <v>12</v>
       </c>
@@ -17858,7 +17836,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:10">
       <c r="A506" t="s">
         <v>47</v>
       </c>
@@ -17890,7 +17868,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:10">
       <c r="A507" t="s">
         <v>47</v>
       </c>
@@ -17922,7 +17900,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:10">
       <c r="A508" t="s">
         <v>47</v>
       </c>
@@ -17954,7 +17932,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:10">
       <c r="A509" t="s">
         <v>47</v>
       </c>
@@ -17986,7 +17964,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:10">
       <c r="A510" t="s">
         <v>47</v>
       </c>
@@ -18018,7 +17996,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:10">
       <c r="A511" t="s">
         <v>47</v>
       </c>
@@ -18050,7 +18028,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:10">
       <c r="A512" t="s">
         <v>47</v>
       </c>
@@ -18082,7 +18060,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10">
       <c r="A513" t="s">
         <v>47</v>
       </c>
@@ -18114,7 +18092,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:10">
       <c r="A514" t="s">
         <v>47</v>
       </c>
@@ -18146,7 +18124,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:10">
       <c r="A515" t="s">
         <v>47</v>
       </c>
@@ -18178,7 +18156,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:10">
       <c r="A516" t="s">
         <v>47</v>
       </c>
@@ -18210,7 +18188,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:10">
       <c r="A517" t="s">
         <v>47</v>
       </c>
@@ -18242,7 +18220,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:10">
       <c r="A518" t="s">
         <v>40</v>
       </c>
@@ -18274,7 +18252,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:10">
       <c r="A519" t="s">
         <v>40</v>
       </c>
@@ -18306,7 +18284,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:10">
       <c r="A520" t="s">
         <v>40</v>
       </c>
@@ -18338,7 +18316,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:10">
       <c r="A521" t="s">
         <v>40</v>
       </c>
@@ -18370,7 +18348,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:10">
       <c r="A522" t="s">
         <v>40</v>
       </c>
@@ -18402,7 +18380,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:10">
       <c r="A523" t="s">
         <v>40</v>
       </c>
@@ -18434,7 +18412,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:10">
       <c r="A524" t="s">
         <v>40</v>
       </c>
@@ -18466,7 +18444,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:10">
       <c r="A525" t="s">
         <v>40</v>
       </c>
@@ -18498,7 +18476,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:10">
       <c r="A526" t="s">
         <v>40</v>
       </c>
@@ -18530,7 +18508,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:10">
       <c r="A527" t="s">
         <v>40</v>
       </c>
@@ -18562,7 +18540,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:10">
       <c r="A528" t="s">
         <v>40</v>
       </c>
@@ -18594,7 +18572,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:10">
       <c r="A529" t="s">
         <v>40</v>
       </c>
@@ -18626,7 +18604,7 @@
         <v>45904</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:10">
       <c r="A530" t="s">
         <v>26</v>
       </c>
@@ -18658,7 +18636,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:10">
       <c r="A531" t="s">
         <v>26</v>
       </c>
@@ -18690,7 +18668,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:10">
       <c r="A532" t="s">
         <v>26</v>
       </c>
@@ -18722,7 +18700,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:10">
       <c r="A533" t="s">
         <v>26</v>
       </c>
@@ -18754,7 +18732,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:10">
       <c r="A534" t="s">
         <v>26</v>
       </c>
@@ -18786,7 +18764,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:10">
       <c r="A535" t="s">
         <v>26</v>
       </c>
@@ -18818,7 +18796,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:10">
       <c r="A536" t="s">
         <v>26</v>
       </c>
@@ -18850,7 +18828,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:10">
       <c r="A537" t="s">
         <v>26</v>
       </c>
@@ -18882,7 +18860,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:10">
       <c r="A538" t="s">
         <v>26</v>
       </c>
@@ -18914,7 +18892,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:10">
       <c r="A539" t="s">
         <v>26</v>
       </c>
@@ -18946,7 +18924,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:10">
       <c r="A540" t="s">
         <v>26</v>
       </c>
@@ -18978,7 +18956,7 @@
         <v>45911</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:10">
       <c r="A541" t="s">
         <v>26</v>
       </c>
@@ -19010,7 +18988,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:10">
       <c r="A542" t="s">
         <v>12</v>
       </c>
@@ -19042,7 +19020,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:10">
       <c r="A543" t="s">
         <v>12</v>
       </c>
@@ -19074,7 +19052,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:10">
       <c r="A544" t="s">
         <v>12</v>
       </c>
@@ -19106,7 +19084,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:10">
       <c r="A545" t="s">
         <v>12</v>
       </c>
@@ -19138,7 +19116,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:10">
       <c r="A546" t="s">
         <v>12</v>
       </c>
@@ -19170,7 +19148,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:10">
       <c r="A547" t="s">
         <v>12</v>
       </c>
@@ -19202,7 +19180,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:10">
       <c r="A548" t="s">
         <v>12</v>
       </c>
@@ -19234,7 +19212,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:10">
       <c r="A549" t="s">
         <v>12</v>
       </c>
@@ -19266,7 +19244,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:10">
       <c r="A550" t="s">
         <v>12</v>
       </c>
@@ -19298,7 +19276,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:10">
       <c r="A551" t="s">
         <v>12</v>
       </c>
@@ -19330,7 +19308,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:10">
       <c r="A552" t="s">
         <v>12</v>
       </c>
@@ -19362,7 +19340,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:10">
       <c r="A553" t="s">
         <v>12</v>
       </c>
@@ -19394,7 +19372,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:10">
       <c r="A554" t="s">
         <v>47</v>
       </c>
@@ -19426,7 +19404,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:10">
       <c r="A555" t="s">
         <v>47</v>
       </c>
@@ -19458,7 +19436,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:10">
       <c r="A556" t="s">
         <v>47</v>
       </c>
@@ -19490,7 +19468,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:10">
       <c r="A557" t="s">
         <v>47</v>
       </c>
@@ -19522,7 +19500,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:10">
       <c r="A558" t="s">
         <v>47</v>
       </c>
@@ -19554,7 +19532,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:10">
       <c r="A559" t="s">
         <v>47</v>
       </c>
@@ -19586,7 +19564,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:10">
       <c r="A560" t="s">
         <v>47</v>
       </c>
@@ -19618,7 +19596,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:10">
       <c r="A561" t="s">
         <v>47</v>
       </c>
@@ -19650,7 +19628,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:10">
       <c r="A562" t="s">
         <v>47</v>
       </c>
@@ -19682,7 +19660,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:10">
       <c r="A563" t="s">
         <v>47</v>
       </c>
@@ -19714,7 +19692,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:10">
       <c r="A564" t="s">
         <v>47</v>
       </c>
@@ -19746,7 +19724,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:10">
       <c r="A565" t="s">
         <v>47</v>
       </c>
@@ -19778,7 +19756,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:10">
       <c r="A566" t="s">
         <v>40</v>
       </c>
@@ -19810,7 +19788,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:10">
       <c r="A567" t="s">
         <v>40</v>
       </c>
@@ -19842,7 +19820,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:10">
       <c r="A568" t="s">
         <v>40</v>
       </c>
@@ -19874,7 +19852,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:10">
       <c r="A569" t="s">
         <v>40</v>
       </c>
@@ -19906,7 +19884,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:10">
       <c r="A570" t="s">
         <v>40</v>
       </c>
@@ -19938,7 +19916,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:10">
       <c r="A571" t="s">
         <v>40</v>
       </c>
@@ -19970,7 +19948,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:10">
       <c r="A572" t="s">
         <v>40</v>
       </c>
@@ -20002,7 +19980,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:10">
       <c r="A573" t="s">
         <v>40</v>
       </c>
@@ -20034,7 +20012,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:10">
       <c r="A574" t="s">
         <v>40</v>
       </c>
@@ -20066,7 +20044,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:10">
       <c r="A575" t="s">
         <v>40</v>
       </c>
@@ -20098,7 +20076,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:10">
       <c r="A576" t="s">
         <v>40</v>
       </c>
@@ -20130,7 +20108,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:10">
       <c r="A577" t="s">
         <v>40</v>
       </c>
@@ -20162,7 +20140,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:10">
       <c r="A578" t="s">
         <v>23</v>
       </c>
@@ -20194,7 +20172,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:10">
       <c r="A579" t="s">
         <v>23</v>
       </c>
@@ -20226,7 +20204,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:10">
       <c r="A580" t="s">
         <v>23</v>
       </c>
@@ -20258,7 +20236,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:10">
       <c r="A581" t="s">
         <v>23</v>
       </c>
@@ -20290,7 +20268,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:10">
       <c r="A582" t="s">
         <v>23</v>
       </c>
@@ -20322,7 +20300,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:10">
       <c r="A583" t="s">
         <v>23</v>
       </c>
@@ -20354,7 +20332,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:10">
       <c r="A584" t="s">
         <v>23</v>
       </c>
@@ -20386,7 +20364,7 @@
         <v>45911</v>
       </c>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:10">
       <c r="A585" t="s">
         <v>23</v>
       </c>
@@ -20418,7 +20396,7 @@
         <v>45742</v>
       </c>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:10">
       <c r="A586" t="s">
         <v>23</v>
       </c>
@@ -20450,7 +20428,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:10">
       <c r="A587" t="s">
         <v>23</v>
       </c>
@@ -20482,7 +20460,7 @@
         <v>45686</v>
       </c>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:10">
       <c r="A588" t="s">
         <v>23</v>
       </c>
@@ -20514,7 +20492,7 @@
         <v>45675</v>
       </c>
     </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:10">
       <c r="A589" t="s">
         <v>23</v>
       </c>
@@ -20546,7 +20524,7 @@
         <v>45668</v>
       </c>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:10">
       <c r="A590" t="s">
         <v>20</v>
       </c>
@@ -20578,7 +20556,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:10">
       <c r="A591" t="s">
         <v>20</v>
       </c>
@@ -20610,7 +20588,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:10">
       <c r="A592" t="s">
         <v>20</v>
       </c>
@@ -20642,7 +20620,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:10">
       <c r="A593" t="s">
         <v>20</v>
       </c>
@@ -20674,7 +20652,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:10">
       <c r="A594" t="s">
         <v>20</v>
       </c>
@@ -20706,7 +20684,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:10">
       <c r="A595" t="s">
         <v>20</v>
       </c>
@@ -20738,7 +20716,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:10">
       <c r="A596" t="s">
         <v>20</v>
       </c>
@@ -20770,7 +20748,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:10">
       <c r="A597" t="s">
         <v>20</v>
       </c>
@@ -20802,7 +20780,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:10">
       <c r="A598" t="s">
         <v>20</v>
       </c>
@@ -20834,7 +20812,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:10">
       <c r="A599" t="s">
         <v>20</v>
       </c>
@@ -20866,7 +20844,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:10">
       <c r="A600" t="s">
         <v>20</v>
       </c>
@@ -20898,7 +20876,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:10">
       <c r="A601" t="s">
         <v>20</v>
       </c>
@@ -20930,7 +20908,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:10">
       <c r="A602" t="s">
         <v>45</v>
       </c>
@@ -20962,7 +20940,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:10">
       <c r="A603" t="s">
         <v>45</v>
       </c>
@@ -20994,7 +20972,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:10">
       <c r="A604" t="s">
         <v>45</v>
       </c>
@@ -21026,7 +21004,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:10">
       <c r="A605" t="s">
         <v>45</v>
       </c>
@@ -21058,7 +21036,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:10">
       <c r="A606" t="s">
         <v>45</v>
       </c>
@@ -21090,7 +21068,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:10">
       <c r="A607" t="s">
         <v>45</v>
       </c>
@@ -21122,7 +21100,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:10">
       <c r="A608" t="s">
         <v>45</v>
       </c>
@@ -21154,7 +21132,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="609" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:10">
       <c r="A609" t="s">
         <v>45</v>
       </c>
@@ -21186,7 +21164,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="610" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:10">
       <c r="A610" t="s">
         <v>45</v>
       </c>
@@ -21218,7 +21196,7 @@
         <v>45740</v>
       </c>
     </row>
-    <row r="611" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:10">
       <c r="A611" t="s">
         <v>45</v>
       </c>
@@ -21250,7 +21228,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="612" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:10">
       <c r="A612" t="s">
         <v>45</v>
       </c>
@@ -21282,7 +21260,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="613" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:10">
       <c r="A613" t="s">
         <v>45</v>
       </c>
@@ -21314,7 +21292,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="614" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:10">
       <c r="A614" t="s">
         <v>9</v>
       </c>
@@ -21346,7 +21324,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="615" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:10">
       <c r="A615" t="s">
         <v>9</v>
       </c>
@@ -21378,7 +21356,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="616" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:10">
       <c r="A616" t="s">
         <v>9</v>
       </c>
@@ -21410,7 +21388,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="617" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:10">
       <c r="A617" t="s">
         <v>9</v>
       </c>
@@ -21442,7 +21420,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="618" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:10">
       <c r="A618" t="s">
         <v>9</v>
       </c>
@@ -21474,7 +21452,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="619" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:10">
       <c r="A619" t="s">
         <v>9</v>
       </c>
@@ -21506,7 +21484,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="620" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:10">
       <c r="A620" t="s">
         <v>9</v>
       </c>
@@ -21538,7 +21516,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="621" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:10">
       <c r="A621" t="s">
         <v>9</v>
       </c>
@@ -21570,7 +21548,7 @@
         <v>45454</v>
       </c>
     </row>
-    <row r="622" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:10">
       <c r="A622" t="s">
         <v>9</v>
       </c>
@@ -21602,7 +21580,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="623" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:10">
       <c r="A623" t="s">
         <v>9</v>
       </c>
@@ -21634,7 +21612,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="624" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:10">
       <c r="A624" t="s">
         <v>9</v>
       </c>
@@ -21666,7 +21644,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:10">
       <c r="A625" t="s">
         <v>9</v>
       </c>
@@ -21698,7 +21676,7 @@
         <v>45577</v>
       </c>
     </row>
-    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:10">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -21730,7 +21708,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:10">
       <c r="A627" t="s">
         <v>49</v>
       </c>
@@ -21762,7 +21740,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:10">
       <c r="A628" t="s">
         <v>35</v>
       </c>
@@ -21794,7 +21772,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:10">
       <c r="A629" t="s">
         <v>27</v>
       </c>
@@ -21826,7 +21804,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:10">
       <c r="A630" t="s">
         <v>4</v>
       </c>
@@ -21858,7 +21836,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:10">
       <c r="A631" t="s">
         <v>81</v>
       </c>
@@ -21890,7 +21868,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:10">
       <c r="A632" t="s">
         <v>30</v>
       </c>
@@ -21922,7 +21900,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:10">
       <c r="A633" t="s">
         <v>34</v>
       </c>
@@ -21954,7 +21932,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:10">
       <c r="A634" t="s">
         <v>11</v>
       </c>
@@ -21986,7 +21964,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:10">
       <c r="A635" t="s">
         <v>46</v>
       </c>
@@ -22018,7 +21996,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:10">
       <c r="A636" t="s">
         <v>28</v>
       </c>
@@ -22050,7 +22028,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:10">
       <c r="A637" t="s">
         <v>8</v>
       </c>
@@ -22082,7 +22060,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:10">
       <c r="A638" t="s">
         <v>5</v>
       </c>
@@ -22114,7 +22092,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:10">
       <c r="A639" t="s">
         <v>14</v>
       </c>
@@ -22146,7 +22124,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:10">
       <c r="A640" t="s">
         <v>33</v>
       </c>
@@ -22178,7 +22156,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:10">
       <c r="A641" t="s">
         <v>31</v>
       </c>
@@ -22210,7 +22188,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:10">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -22242,7 +22220,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:10">
       <c r="A643" t="s">
         <v>7</v>
       </c>
@@ -22274,7 +22252,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:10">
       <c r="A644" t="s">
         <v>43</v>
       </c>
@@ -22306,7 +22284,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:10">
       <c r="A645" t="s">
         <v>13</v>
       </c>
@@ -22338,7 +22316,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:10">
       <c r="A646" t="s">
         <v>25</v>
       </c>
@@ -22370,7 +22348,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:10">
       <c r="A647" t="s">
         <v>38</v>
       </c>
@@ -22402,7 +22380,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:10">
       <c r="A648" t="s">
         <v>29</v>
       </c>
@@ -22434,7 +22412,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:10">
       <c r="A649" t="s">
         <v>50</v>
       </c>
@@ -22466,7 +22444,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:10">
       <c r="A650" t="s">
         <v>18</v>
       </c>
@@ -22498,7 +22476,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:10">
       <c r="A651" t="s">
         <v>44</v>
       </c>
@@ -22530,7 +22508,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:10">
       <c r="A652" t="s">
         <v>37</v>
       </c>
@@ -22562,7 +22540,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:10">
       <c r="A653" t="s">
         <v>51</v>
       </c>
@@ -22594,7 +22572,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:10">
       <c r="A654" t="s">
         <v>21</v>
       </c>
@@ -22626,7 +22604,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:10">
       <c r="A655" t="s">
         <v>42</v>
       </c>
@@ -22658,7 +22636,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:10">
       <c r="A656" t="s">
         <v>32</v>
       </c>
@@ -22690,7 +22668,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="657" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:10">
       <c r="A657" t="s">
         <v>15</v>
       </c>
@@ -22722,7 +22700,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="658" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:10">
       <c r="A658" t="s">
         <v>22</v>
       </c>
@@ -22754,7 +22732,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="659" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:10">
       <c r="A659" t="s">
         <v>48</v>
       </c>
@@ -22786,7 +22764,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="660" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:10">
       <c r="A660" t="s">
         <v>24</v>
       </c>
@@ -22818,7 +22796,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="661" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:10">
       <c r="A661" t="s">
         <v>36</v>
       </c>
@@ -22850,7 +22828,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="662" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:10">
       <c r="A662" t="s">
         <v>10</v>
       </c>
@@ -22882,7 +22860,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="663" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:10">
       <c r="A663" t="s">
         <v>41</v>
       </c>
@@ -22914,7 +22892,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="664" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:10">
       <c r="A664" t="s">
         <v>17</v>
       </c>
@@ -22946,7 +22924,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="665" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:10">
       <c r="A665" t="s">
         <v>39</v>
       </c>
@@ -22978,7 +22956,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="666" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:10">
       <c r="A666" t="s">
         <v>26</v>
       </c>
@@ -23010,7 +22988,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:10">
       <c r="A667" t="s">
         <v>47</v>
       </c>
@@ -23042,7 +23020,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:10">
       <c r="A668" t="s">
         <v>12</v>
       </c>
@@ -23074,7 +23052,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:10">
       <c r="A669" t="s">
         <v>40</v>
       </c>
@@ -23106,7 +23084,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:10">
       <c r="A670" t="s">
         <v>23</v>
       </c>
@@ -23138,7 +23116,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:10">
       <c r="A671" t="s">
         <v>20</v>
       </c>
@@ -23170,7 +23148,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:10">
       <c r="A672" t="s">
         <v>45</v>
       </c>
@@ -23202,7 +23180,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:10">
       <c r="A673" t="s">
         <v>9</v>
       </c>
@@ -23234,8 +23212,3079 @@
         <v>46191</v>
       </c>
     </row>
+    <row r="674" spans="1:10">
+      <c r="A674" t="s">
+        <v>27</v>
+      </c>
+      <c r="B674" t="s">
+        <v>49</v>
+      </c>
+      <c r="C674" t="s">
+        <v>191</v>
+      </c>
+      <c r="D674">
+        <v>1</v>
+      </c>
+      <c r="E674">
+        <v>1</v>
+      </c>
+      <c r="F674">
+        <v>0</v>
+      </c>
+      <c r="G674" t="s">
+        <v>205</v>
+      </c>
+      <c r="H674" t="s">
+        <v>208</v>
+      </c>
+      <c r="I674">
+        <v>0</v>
+      </c>
+      <c r="J674" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="675" spans="1:10">
+      <c r="A675" t="s">
+        <v>49</v>
+      </c>
+      <c r="B675" t="s">
+        <v>27</v>
+      </c>
+      <c r="C675" t="s">
+        <v>191</v>
+      </c>
+      <c r="D675">
+        <v>1</v>
+      </c>
+      <c r="E675">
+        <v>1</v>
+      </c>
+      <c r="F675">
+        <v>0</v>
+      </c>
+      <c r="G675" t="s">
+        <v>205</v>
+      </c>
+      <c r="H675" t="s">
+        <v>208</v>
+      </c>
+      <c r="I675">
+        <v>0</v>
+      </c>
+      <c r="J675" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="676" spans="1:10">
+      <c r="A676" t="s">
+        <v>6</v>
+      </c>
+      <c r="B676" t="s">
+        <v>35</v>
+      </c>
+      <c r="C676" t="s">
+        <v>193</v>
+      </c>
+      <c r="D676">
+        <v>1</v>
+      </c>
+      <c r="E676">
+        <v>0</v>
+      </c>
+      <c r="F676">
+        <v>1</v>
+      </c>
+      <c r="G676" t="s">
+        <v>205</v>
+      </c>
+      <c r="H676" t="s">
+        <v>207</v>
+      </c>
+      <c r="I676">
+        <v>1</v>
+      </c>
+      <c r="J676" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="677" spans="1:10">
+      <c r="A677" t="s">
+        <v>35</v>
+      </c>
+      <c r="B677" t="s">
+        <v>6</v>
+      </c>
+      <c r="C677" t="s">
+        <v>192</v>
+      </c>
+      <c r="D677">
+        <v>0</v>
+      </c>
+      <c r="E677">
+        <v>1</v>
+      </c>
+      <c r="F677">
+        <v>-1</v>
+      </c>
+      <c r="G677" t="s">
+        <v>205</v>
+      </c>
+      <c r="H677" t="s">
+        <v>206</v>
+      </c>
+      <c r="I677">
+        <v>0</v>
+      </c>
+      <c r="J677" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="678" spans="1:10">
+      <c r="A678" t="s">
+        <v>30</v>
+      </c>
+      <c r="B678" t="s">
+        <v>81</v>
+      </c>
+      <c r="C678" t="s">
+        <v>191</v>
+      </c>
+      <c r="D678">
+        <v>4</v>
+      </c>
+      <c r="E678">
+        <v>1</v>
+      </c>
+      <c r="F678">
+        <v>3</v>
+      </c>
+      <c r="G678" t="s">
+        <v>205</v>
+      </c>
+      <c r="H678" t="s">
+        <v>207</v>
+      </c>
+      <c r="I678">
+        <v>0</v>
+      </c>
+      <c r="J678" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="679" spans="1:10">
+      <c r="A679" t="s">
+        <v>81</v>
+      </c>
+      <c r="B679" t="s">
+        <v>30</v>
+      </c>
+      <c r="C679" t="s">
+        <v>191</v>
+      </c>
+      <c r="D679">
+        <v>1</v>
+      </c>
+      <c r="E679">
+        <v>4</v>
+      </c>
+      <c r="F679">
+        <v>-3</v>
+      </c>
+      <c r="G679" t="s">
+        <v>205</v>
+      </c>
+      <c r="H679" t="s">
+        <v>206</v>
+      </c>
+      <c r="I679">
+        <v>0</v>
+      </c>
+      <c r="J679" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="680" spans="1:10">
+      <c r="A680" t="s">
+        <v>4</v>
+      </c>
+      <c r="B680" t="s">
+        <v>34</v>
+      </c>
+      <c r="C680" t="s">
+        <v>193</v>
+      </c>
+      <c r="D680">
+        <v>6</v>
+      </c>
+      <c r="E680">
+        <v>0</v>
+      </c>
+      <c r="F680">
+        <v>6</v>
+      </c>
+      <c r="G680" t="s">
+        <v>205</v>
+      </c>
+      <c r="H680" t="s">
+        <v>207</v>
+      </c>
+      <c r="I680">
+        <v>1</v>
+      </c>
+      <c r="J680" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="681" spans="1:10">
+      <c r="A681" t="s">
+        <v>34</v>
+      </c>
+      <c r="B681" t="s">
+        <v>4</v>
+      </c>
+      <c r="C681" t="s">
+        <v>192</v>
+      </c>
+      <c r="D681">
+        <v>0</v>
+      </c>
+      <c r="E681">
+        <v>6</v>
+      </c>
+      <c r="F681">
+        <v>-6</v>
+      </c>
+      <c r="G681" t="s">
+        <v>205</v>
+      </c>
+      <c r="H681" t="s">
+        <v>206</v>
+      </c>
+      <c r="I681">
+        <v>0</v>
+      </c>
+      <c r="J681" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="682" spans="1:10">
+      <c r="A682" t="s">
+        <v>46</v>
+      </c>
+      <c r="B682" t="s">
+        <v>28</v>
+      </c>
+      <c r="C682" t="s">
+        <v>191</v>
+      </c>
+      <c r="D682">
+        <v>1</v>
+      </c>
+      <c r="E682">
+        <v>0</v>
+      </c>
+      <c r="F682">
+        <v>1</v>
+      </c>
+      <c r="G682" t="s">
+        <v>205</v>
+      </c>
+      <c r="H682" t="s">
+        <v>207</v>
+      </c>
+      <c r="I682">
+        <v>1</v>
+      </c>
+      <c r="J682" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="683" spans="1:10">
+      <c r="A683" t="s">
+        <v>28</v>
+      </c>
+      <c r="B683" t="s">
+        <v>46</v>
+      </c>
+      <c r="C683" t="s">
+        <v>191</v>
+      </c>
+      <c r="D683">
+        <v>0</v>
+      </c>
+      <c r="E683">
+        <v>1</v>
+      </c>
+      <c r="F683">
+        <v>-1</v>
+      </c>
+      <c r="G683" t="s">
+        <v>205</v>
+      </c>
+      <c r="H683" t="s">
+        <v>206</v>
+      </c>
+      <c r="I683">
+        <v>0</v>
+      </c>
+      <c r="J683" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="684" spans="1:10">
+      <c r="A684" t="s">
+        <v>11</v>
+      </c>
+      <c r="B684" t="s">
+        <v>8</v>
+      </c>
+      <c r="C684" t="s">
+        <v>191</v>
+      </c>
+      <c r="D684">
+        <v>3</v>
+      </c>
+      <c r="E684">
+        <v>0</v>
+      </c>
+      <c r="F684">
+        <v>3</v>
+      </c>
+      <c r="G684" t="s">
+        <v>205</v>
+      </c>
+      <c r="H684" t="s">
+        <v>207</v>
+      </c>
+      <c r="I684">
+        <v>1</v>
+      </c>
+      <c r="J684" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="685" spans="1:10">
+      <c r="A685" t="s">
+        <v>8</v>
+      </c>
+      <c r="B685" t="s">
+        <v>11</v>
+      </c>
+      <c r="C685" t="s">
+        <v>191</v>
+      </c>
+      <c r="D685">
+        <v>0</v>
+      </c>
+      <c r="E685">
+        <v>3</v>
+      </c>
+      <c r="F685">
+        <v>-3</v>
+      </c>
+      <c r="G685" t="s">
+        <v>205</v>
+      </c>
+      <c r="H685" t="s">
+        <v>206</v>
+      </c>
+      <c r="I685">
+        <v>0</v>
+      </c>
+      <c r="J685" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="686" spans="1:10">
+      <c r="A686" t="s">
+        <v>5</v>
+      </c>
+      <c r="B686" t="s">
+        <v>33</v>
+      </c>
+      <c r="C686" t="s">
+        <v>193</v>
+      </c>
+      <c r="D686">
+        <v>2</v>
+      </c>
+      <c r="E686">
+        <v>0</v>
+      </c>
+      <c r="F686">
+        <v>2</v>
+      </c>
+      <c r="G686" t="s">
+        <v>205</v>
+      </c>
+      <c r="H686" t="s">
+        <v>207</v>
+      </c>
+      <c r="I686">
+        <v>1</v>
+      </c>
+      <c r="J686" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="687" spans="1:10">
+      <c r="A687" t="s">
+        <v>33</v>
+      </c>
+      <c r="B687" t="s">
+        <v>5</v>
+      </c>
+      <c r="C687" t="s">
+        <v>192</v>
+      </c>
+      <c r="D687">
+        <v>0</v>
+      </c>
+      <c r="E687">
+        <v>2</v>
+      </c>
+      <c r="F687">
+        <v>-2</v>
+      </c>
+      <c r="G687" t="s">
+        <v>205</v>
+      </c>
+      <c r="H687" t="s">
+        <v>206</v>
+      </c>
+      <c r="I687">
+        <v>0</v>
+      </c>
+      <c r="J687" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="688" spans="1:10">
+      <c r="A688" t="s">
+        <v>14</v>
+      </c>
+      <c r="B688" t="s">
+        <v>31</v>
+      </c>
+      <c r="C688" t="s">
+        <v>191</v>
+      </c>
+      <c r="D688">
+        <v>1</v>
+      </c>
+      <c r="E688">
+        <v>0</v>
+      </c>
+      <c r="F688">
+        <v>1</v>
+      </c>
+      <c r="G688" t="s">
+        <v>205</v>
+      </c>
+      <c r="H688" t="s">
+        <v>207</v>
+      </c>
+      <c r="I688">
+        <v>1</v>
+      </c>
+      <c r="J688" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="689" spans="1:10">
+      <c r="A689" t="s">
+        <v>31</v>
+      </c>
+      <c r="B689" t="s">
+        <v>14</v>
+      </c>
+      <c r="C689" t="s">
+        <v>191</v>
+      </c>
+      <c r="D689">
+        <v>0</v>
+      </c>
+      <c r="E689">
+        <v>1</v>
+      </c>
+      <c r="F689">
+        <v>-1</v>
+      </c>
+      <c r="G689" t="s">
+        <v>205</v>
+      </c>
+      <c r="H689" t="s">
+        <v>206</v>
+      </c>
+      <c r="I689">
+        <v>0</v>
+      </c>
+      <c r="J689" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="690" spans="1:10">
+      <c r="A690" t="s">
+        <v>16</v>
+      </c>
+      <c r="B690" t="s">
+        <v>43</v>
+      </c>
+      <c r="C690" t="s">
+        <v>191</v>
+      </c>
+      <c r="D690">
+        <v>2</v>
+      </c>
+      <c r="E690">
+        <v>1</v>
+      </c>
+      <c r="F690">
+        <v>1</v>
+      </c>
+      <c r="G690" t="s">
+        <v>205</v>
+      </c>
+      <c r="H690" t="s">
+        <v>207</v>
+      </c>
+      <c r="I690">
+        <v>0</v>
+      </c>
+      <c r="J690" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="691" spans="1:10">
+      <c r="A691" t="s">
+        <v>43</v>
+      </c>
+      <c r="B691" t="s">
+        <v>16</v>
+      </c>
+      <c r="C691" t="s">
+        <v>191</v>
+      </c>
+      <c r="D691">
+        <v>1</v>
+      </c>
+      <c r="E691">
+        <v>2</v>
+      </c>
+      <c r="F691">
+        <v>-1</v>
+      </c>
+      <c r="G691" t="s">
+        <v>205</v>
+      </c>
+      <c r="H691" t="s">
+        <v>206</v>
+      </c>
+      <c r="I691">
+        <v>0</v>
+      </c>
+      <c r="J691" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="692" spans="1:10">
+      <c r="A692" t="s">
+        <v>13</v>
+      </c>
+      <c r="B692" t="s">
+        <v>7</v>
+      </c>
+      <c r="C692" t="s">
+        <v>191</v>
+      </c>
+      <c r="D692">
+        <v>0</v>
+      </c>
+      <c r="E692">
+        <v>0</v>
+      </c>
+      <c r="F692">
+        <v>0</v>
+      </c>
+      <c r="G692" t="s">
+        <v>205</v>
+      </c>
+      <c r="H692" t="s">
+        <v>208</v>
+      </c>
+      <c r="I692">
+        <v>1</v>
+      </c>
+      <c r="J692" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="693" spans="1:10">
+      <c r="A693" t="s">
+        <v>7</v>
+      </c>
+      <c r="B693" t="s">
+        <v>13</v>
+      </c>
+      <c r="C693" t="s">
+        <v>191</v>
+      </c>
+      <c r="D693">
+        <v>0</v>
+      </c>
+      <c r="E693">
+        <v>0</v>
+      </c>
+      <c r="F693">
+        <v>0</v>
+      </c>
+      <c r="G693" t="s">
+        <v>205</v>
+      </c>
+      <c r="H693" t="s">
+        <v>208</v>
+      </c>
+      <c r="I693">
+        <v>1</v>
+      </c>
+      <c r="J693" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="694" spans="1:10">
+      <c r="A694" t="s">
+        <v>25</v>
+      </c>
+      <c r="B694" t="s">
+        <v>29</v>
+      </c>
+      <c r="C694" t="s">
+        <v>191</v>
+      </c>
+      <c r="D694">
+        <v>5</v>
+      </c>
+      <c r="E694">
+        <v>1</v>
+      </c>
+      <c r="F694">
+        <v>4</v>
+      </c>
+      <c r="G694" t="s">
+        <v>205</v>
+      </c>
+      <c r="H694" t="s">
+        <v>207</v>
+      </c>
+      <c r="I694">
+        <v>0</v>
+      </c>
+      <c r="J694" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="695" spans="1:10">
+      <c r="A695" t="s">
+        <v>29</v>
+      </c>
+      <c r="B695" t="s">
+        <v>25</v>
+      </c>
+      <c r="C695" t="s">
+        <v>191</v>
+      </c>
+      <c r="D695">
+        <v>1</v>
+      </c>
+      <c r="E695">
+        <v>5</v>
+      </c>
+      <c r="F695">
+        <v>-4</v>
+      </c>
+      <c r="G695" t="s">
+        <v>205</v>
+      </c>
+      <c r="H695" t="s">
+        <v>206</v>
+      </c>
+      <c r="I695">
+        <v>0</v>
+      </c>
+      <c r="J695" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="696" spans="1:10">
+      <c r="A696" t="s">
+        <v>38</v>
+      </c>
+      <c r="B696" t="s">
+        <v>50</v>
+      </c>
+      <c r="C696" t="s">
+        <v>191</v>
+      </c>
+      <c r="D696">
+        <v>4</v>
+      </c>
+      <c r="E696">
+        <v>0</v>
+      </c>
+      <c r="F696">
+        <v>4</v>
+      </c>
+      <c r="G696" t="s">
+        <v>205</v>
+      </c>
+      <c r="H696" t="s">
+        <v>207</v>
+      </c>
+      <c r="I696">
+        <v>1</v>
+      </c>
+      <c r="J696" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="697" spans="1:10">
+      <c r="A697" t="s">
+        <v>50</v>
+      </c>
+      <c r="B697" t="s">
+        <v>38</v>
+      </c>
+      <c r="C697" t="s">
+        <v>191</v>
+      </c>
+      <c r="D697">
+        <v>0</v>
+      </c>
+      <c r="E697">
+        <v>4</v>
+      </c>
+      <c r="F697">
+        <v>-4</v>
+      </c>
+      <c r="G697" t="s">
+        <v>205</v>
+      </c>
+      <c r="H697" t="s">
+        <v>206</v>
+      </c>
+      <c r="I697">
+        <v>0</v>
+      </c>
+      <c r="J697" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="698" spans="1:10">
+      <c r="A698" t="s">
+        <v>18</v>
+      </c>
+      <c r="B698" t="s">
+        <v>37</v>
+      </c>
+      <c r="C698" t="s">
+        <v>191</v>
+      </c>
+      <c r="D698">
+        <v>0</v>
+      </c>
+      <c r="E698">
+        <v>0</v>
+      </c>
+      <c r="F698">
+        <v>0</v>
+      </c>
+      <c r="G698" t="s">
+        <v>205</v>
+      </c>
+      <c r="H698" t="s">
+        <v>208</v>
+      </c>
+      <c r="I698">
+        <v>1</v>
+      </c>
+      <c r="J698" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="699" spans="1:10">
+      <c r="A699" t="s">
+        <v>37</v>
+      </c>
+      <c r="B699" t="s">
+        <v>18</v>
+      </c>
+      <c r="C699" t="s">
+        <v>191</v>
+      </c>
+      <c r="D699">
+        <v>0</v>
+      </c>
+      <c r="E699">
+        <v>0</v>
+      </c>
+      <c r="F699">
+        <v>0</v>
+      </c>
+      <c r="G699" t="s">
+        <v>205</v>
+      </c>
+      <c r="H699" t="s">
+        <v>208</v>
+      </c>
+      <c r="I699">
+        <v>1</v>
+      </c>
+      <c r="J699" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="700" spans="1:10">
+      <c r="A700" t="s">
+        <v>44</v>
+      </c>
+      <c r="B700" t="s">
+        <v>51</v>
+      </c>
+      <c r="C700" t="s">
+        <v>191</v>
+      </c>
+      <c r="D700">
+        <v>3</v>
+      </c>
+      <c r="E700">
+        <v>1</v>
+      </c>
+      <c r="F700">
+        <v>2</v>
+      </c>
+      <c r="G700" t="s">
+        <v>205</v>
+      </c>
+      <c r="H700" t="s">
+        <v>207</v>
+      </c>
+      <c r="I700">
+        <v>0</v>
+      </c>
+      <c r="J700" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="701" spans="1:10">
+      <c r="A701" t="s">
+        <v>51</v>
+      </c>
+      <c r="B701" t="s">
+        <v>44</v>
+      </c>
+      <c r="C701" t="s">
+        <v>191</v>
+      </c>
+      <c r="D701">
+        <v>1</v>
+      </c>
+      <c r="E701">
+        <v>3</v>
+      </c>
+      <c r="F701">
+        <v>-2</v>
+      </c>
+      <c r="G701" t="s">
+        <v>205</v>
+      </c>
+      <c r="H701" t="s">
+        <v>206</v>
+      </c>
+      <c r="I701">
+        <v>0</v>
+      </c>
+      <c r="J701" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="702" spans="1:10">
+      <c r="A702" t="s">
+        <v>21</v>
+      </c>
+      <c r="B702" t="s">
+        <v>32</v>
+      </c>
+      <c r="C702" t="s">
+        <v>191</v>
+      </c>
+      <c r="D702">
+        <v>4</v>
+      </c>
+      <c r="E702">
+        <v>0</v>
+      </c>
+      <c r="F702">
+        <v>4</v>
+      </c>
+      <c r="G702" t="s">
+        <v>205</v>
+      </c>
+      <c r="H702" t="s">
+        <v>207</v>
+      </c>
+      <c r="I702">
+        <v>1</v>
+      </c>
+      <c r="J702" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="703" spans="1:10">
+      <c r="A703" t="s">
+        <v>32</v>
+      </c>
+      <c r="B703" t="s">
+        <v>21</v>
+      </c>
+      <c r="C703" t="s">
+        <v>191</v>
+      </c>
+      <c r="D703">
+        <v>0</v>
+      </c>
+      <c r="E703">
+        <v>4</v>
+      </c>
+      <c r="F703">
+        <v>-4</v>
+      </c>
+      <c r="G703" t="s">
+        <v>205</v>
+      </c>
+      <c r="H703" t="s">
+        <v>206</v>
+      </c>
+      <c r="I703">
+        <v>0</v>
+      </c>
+      <c r="J703" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="704" spans="1:10">
+      <c r="A704" t="s">
+        <v>15</v>
+      </c>
+      <c r="B704" t="s">
+        <v>42</v>
+      </c>
+      <c r="C704" t="s">
+        <v>191</v>
+      </c>
+      <c r="D704">
+        <v>2</v>
+      </c>
+      <c r="E704">
+        <v>2</v>
+      </c>
+      <c r="F704">
+        <v>0</v>
+      </c>
+      <c r="G704" t="s">
+        <v>205</v>
+      </c>
+      <c r="H704" t="s">
+        <v>208</v>
+      </c>
+      <c r="I704">
+        <v>0</v>
+      </c>
+      <c r="J704" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="705" spans="1:10">
+      <c r="A705" t="s">
+        <v>42</v>
+      </c>
+      <c r="B705" t="s">
+        <v>15</v>
+      </c>
+      <c r="C705" t="s">
+        <v>191</v>
+      </c>
+      <c r="D705">
+        <v>2</v>
+      </c>
+      <c r="E705">
+        <v>2</v>
+      </c>
+      <c r="F705">
+        <v>0</v>
+      </c>
+      <c r="G705" t="s">
+        <v>205</v>
+      </c>
+      <c r="H705" t="s">
+        <v>208</v>
+      </c>
+      <c r="I705">
+        <v>0</v>
+      </c>
+      <c r="J705" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="706" spans="1:10">
+      <c r="A706" t="s">
+        <v>22</v>
+      </c>
+      <c r="B706" t="s">
+        <v>36</v>
+      </c>
+      <c r="C706" t="s">
+        <v>191</v>
+      </c>
+      <c r="D706">
+        <v>3</v>
+      </c>
+      <c r="E706">
+        <v>0</v>
+      </c>
+      <c r="F706">
+        <v>3</v>
+      </c>
+      <c r="G706" t="s">
+        <v>205</v>
+      </c>
+      <c r="H706" t="s">
+        <v>207</v>
+      </c>
+      <c r="I706">
+        <v>1</v>
+      </c>
+      <c r="J706" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="707" spans="1:10">
+      <c r="A707" t="s">
+        <v>36</v>
+      </c>
+      <c r="B707" t="s">
+        <v>22</v>
+      </c>
+      <c r="C707" t="s">
+        <v>191</v>
+      </c>
+      <c r="D707">
+        <v>0</v>
+      </c>
+      <c r="E707">
+        <v>3</v>
+      </c>
+      <c r="F707">
+        <v>-3</v>
+      </c>
+      <c r="G707" t="s">
+        <v>205</v>
+      </c>
+      <c r="H707" t="s">
+        <v>206</v>
+      </c>
+      <c r="I707">
+        <v>0</v>
+      </c>
+      <c r="J707" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="708" spans="1:10">
+      <c r="A708" t="s">
+        <v>24</v>
+      </c>
+      <c r="B708" t="s">
+        <v>48</v>
+      </c>
+      <c r="C708" t="s">
+        <v>191</v>
+      </c>
+      <c r="D708">
+        <v>3</v>
+      </c>
+      <c r="E708">
+        <v>2</v>
+      </c>
+      <c r="F708">
+        <v>1</v>
+      </c>
+      <c r="G708" t="s">
+        <v>205</v>
+      </c>
+      <c r="H708" t="s">
+        <v>207</v>
+      </c>
+      <c r="I708">
+        <v>0</v>
+      </c>
+      <c r="J708" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="709" spans="1:10">
+      <c r="A709" t="s">
+        <v>48</v>
+      </c>
+      <c r="B709" t="s">
+        <v>24</v>
+      </c>
+      <c r="C709" t="s">
+        <v>191</v>
+      </c>
+      <c r="D709">
+        <v>2</v>
+      </c>
+      <c r="E709">
+        <v>3</v>
+      </c>
+      <c r="F709">
+        <v>-1</v>
+      </c>
+      <c r="G709" t="s">
+        <v>205</v>
+      </c>
+      <c r="H709" t="s">
+        <v>206</v>
+      </c>
+      <c r="I709">
+        <v>0</v>
+      </c>
+      <c r="J709" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="710" spans="1:10">
+      <c r="A710" t="s">
+        <v>10</v>
+      </c>
+      <c r="B710" t="s">
+        <v>17</v>
+      </c>
+      <c r="C710" t="s">
+        <v>191</v>
+      </c>
+      <c r="D710">
+        <v>2</v>
+      </c>
+      <c r="E710">
+        <v>0</v>
+      </c>
+      <c r="F710">
+        <v>2</v>
+      </c>
+      <c r="G710" t="s">
+        <v>205</v>
+      </c>
+      <c r="H710" t="s">
+        <v>207</v>
+      </c>
+      <c r="I710">
+        <v>1</v>
+      </c>
+      <c r="J710" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="711" spans="1:10">
+      <c r="A711" t="s">
+        <v>17</v>
+      </c>
+      <c r="B711" t="s">
+        <v>10</v>
+      </c>
+      <c r="C711" t="s">
+        <v>191</v>
+      </c>
+      <c r="D711">
+        <v>0</v>
+      </c>
+      <c r="E711">
+        <v>2</v>
+      </c>
+      <c r="F711">
+        <v>-2</v>
+      </c>
+      <c r="G711" t="s">
+        <v>205</v>
+      </c>
+      <c r="H711" t="s">
+        <v>206</v>
+      </c>
+      <c r="I711">
+        <v>0</v>
+      </c>
+      <c r="J711" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="712" spans="1:10">
+      <c r="A712" t="s">
+        <v>41</v>
+      </c>
+      <c r="B712" t="s">
+        <v>39</v>
+      </c>
+      <c r="C712" t="s">
+        <v>191</v>
+      </c>
+      <c r="D712">
+        <v>2</v>
+      </c>
+      <c r="E712">
+        <v>1</v>
+      </c>
+      <c r="F712">
+        <v>1</v>
+      </c>
+      <c r="G712" t="s">
+        <v>205</v>
+      </c>
+      <c r="H712" t="s">
+        <v>207</v>
+      </c>
+      <c r="I712">
+        <v>0</v>
+      </c>
+      <c r="J712" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="713" spans="1:10">
+      <c r="A713" t="s">
+        <v>39</v>
+      </c>
+      <c r="B713" t="s">
+        <v>41</v>
+      </c>
+      <c r="C713" t="s">
+        <v>191</v>
+      </c>
+      <c r="D713">
+        <v>1</v>
+      </c>
+      <c r="E713">
+        <v>2</v>
+      </c>
+      <c r="F713">
+        <v>-1</v>
+      </c>
+      <c r="G713" t="s">
+        <v>205</v>
+      </c>
+      <c r="H713" t="s">
+        <v>206</v>
+      </c>
+      <c r="I713">
+        <v>0</v>
+      </c>
+      <c r="J713" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="714" spans="1:10">
+      <c r="A714" t="s">
+        <v>26</v>
+      </c>
+      <c r="B714" t="s">
+        <v>40</v>
+      </c>
+      <c r="C714" t="s">
+        <v>191</v>
+      </c>
+      <c r="D714">
+        <v>5</v>
+      </c>
+      <c r="E714">
+        <v>0</v>
+      </c>
+      <c r="F714">
+        <v>5</v>
+      </c>
+      <c r="G714" t="s">
+        <v>205</v>
+      </c>
+      <c r="H714" t="s">
+        <v>207</v>
+      </c>
+      <c r="I714">
+        <v>1</v>
+      </c>
+      <c r="J714" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="715" spans="1:10">
+      <c r="A715" t="s">
+        <v>40</v>
+      </c>
+      <c r="B715" t="s">
+        <v>26</v>
+      </c>
+      <c r="C715" t="s">
+        <v>191</v>
+      </c>
+      <c r="D715">
+        <v>0</v>
+      </c>
+      <c r="E715">
+        <v>5</v>
+      </c>
+      <c r="F715">
+        <v>-5</v>
+      </c>
+      <c r="G715" t="s">
+        <v>205</v>
+      </c>
+      <c r="H715" t="s">
+        <v>206</v>
+      </c>
+      <c r="I715">
+        <v>0</v>
+      </c>
+      <c r="J715" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="716" spans="1:10">
+      <c r="A716" t="s">
+        <v>12</v>
+      </c>
+      <c r="B716" t="s">
+        <v>47</v>
+      </c>
+      <c r="C716" t="s">
+        <v>191</v>
+      </c>
+      <c r="D716">
+        <v>1</v>
+      </c>
+      <c r="E716">
+        <v>0</v>
+      </c>
+      <c r="F716">
+        <v>1</v>
+      </c>
+      <c r="G716" t="s">
+        <v>205</v>
+      </c>
+      <c r="H716" t="s">
+        <v>207</v>
+      </c>
+      <c r="I716">
+        <v>1</v>
+      </c>
+      <c r="J716" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="717" spans="1:10">
+      <c r="A717" t="s">
+        <v>47</v>
+      </c>
+      <c r="B717" t="s">
+        <v>12</v>
+      </c>
+      <c r="C717" t="s">
+        <v>191</v>
+      </c>
+      <c r="D717">
+        <v>0</v>
+      </c>
+      <c r="E717">
+        <v>1</v>
+      </c>
+      <c r="F717">
+        <v>-1</v>
+      </c>
+      <c r="G717" t="s">
+        <v>205</v>
+      </c>
+      <c r="H717" t="s">
+        <v>206</v>
+      </c>
+      <c r="I717">
+        <v>0</v>
+      </c>
+      <c r="J717" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="718" spans="1:10">
+      <c r="A718" t="s">
+        <v>23</v>
+      </c>
+      <c r="B718" t="s">
+        <v>45</v>
+      </c>
+      <c r="C718" t="s">
+        <v>191</v>
+      </c>
+      <c r="D718">
+        <v>0</v>
+      </c>
+      <c r="E718">
+        <v>0</v>
+      </c>
+      <c r="F718">
+        <v>0</v>
+      </c>
+      <c r="G718" t="s">
+        <v>205</v>
+      </c>
+      <c r="H718" t="s">
+        <v>208</v>
+      </c>
+      <c r="I718">
+        <v>1</v>
+      </c>
+      <c r="J718" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="719" spans="1:10">
+      <c r="A719" t="s">
+        <v>45</v>
+      </c>
+      <c r="B719" t="s">
+        <v>23</v>
+      </c>
+      <c r="C719" t="s">
+        <v>191</v>
+      </c>
+      <c r="D719">
+        <v>0</v>
+      </c>
+      <c r="E719">
+        <v>0</v>
+      </c>
+      <c r="F719">
+        <v>0</v>
+      </c>
+      <c r="G719" t="s">
+        <v>205</v>
+      </c>
+      <c r="H719" t="s">
+        <v>208</v>
+      </c>
+      <c r="I719">
+        <v>1</v>
+      </c>
+      <c r="J719" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="720" spans="1:10">
+      <c r="A720" t="s">
+        <v>20</v>
+      </c>
+      <c r="B720" t="s">
+        <v>9</v>
+      </c>
+      <c r="C720" t="s">
+        <v>191</v>
+      </c>
+      <c r="D720">
+        <v>1</v>
+      </c>
+      <c r="E720">
+        <v>0</v>
+      </c>
+      <c r="F720">
+        <v>1</v>
+      </c>
+      <c r="G720" t="s">
+        <v>205</v>
+      </c>
+      <c r="H720" t="s">
+        <v>207</v>
+      </c>
+      <c r="I720">
+        <v>1</v>
+      </c>
+      <c r="J720" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10">
+      <c r="A721" t="s">
+        <v>9</v>
+      </c>
+      <c r="B721" t="s">
+        <v>20</v>
+      </c>
+      <c r="C721" t="s">
+        <v>191</v>
+      </c>
+      <c r="D721">
+        <v>0</v>
+      </c>
+      <c r="E721">
+        <v>1</v>
+      </c>
+      <c r="F721">
+        <v>-1</v>
+      </c>
+      <c r="G721" t="s">
+        <v>205</v>
+      </c>
+      <c r="H721" t="s">
+        <v>206</v>
+      </c>
+      <c r="I721">
+        <v>0</v>
+      </c>
+      <c r="J721" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10">
+      <c r="A722" t="s">
+        <v>6</v>
+      </c>
+      <c r="B722" t="s">
+        <v>27</v>
+      </c>
+      <c r="C722" t="s">
+        <v>193</v>
+      </c>
+      <c r="D722">
+        <v>3</v>
+      </c>
+      <c r="E722">
+        <v>0</v>
+      </c>
+      <c r="F722">
+        <v>3</v>
+      </c>
+      <c r="G722" t="s">
+        <v>205</v>
+      </c>
+      <c r="H722" t="s">
+        <v>207</v>
+      </c>
+      <c r="I722">
+        <v>1</v>
+      </c>
+      <c r="J722" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="723" spans="1:10">
+      <c r="A723" t="s">
+        <v>27</v>
+      </c>
+      <c r="B723" t="s">
+        <v>6</v>
+      </c>
+      <c r="C723" t="s">
+        <v>192</v>
+      </c>
+      <c r="D723">
+        <v>0</v>
+      </c>
+      <c r="E723">
+        <v>3</v>
+      </c>
+      <c r="F723">
+        <v>-3</v>
+      </c>
+      <c r="G723" t="s">
+        <v>205</v>
+      </c>
+      <c r="H723" t="s">
+        <v>206</v>
+      </c>
+      <c r="I723">
+        <v>0</v>
+      </c>
+      <c r="J723" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="724" spans="1:10">
+      <c r="A724" t="s">
+        <v>49</v>
+      </c>
+      <c r="B724" t="s">
+        <v>35</v>
+      </c>
+      <c r="C724" t="s">
+        <v>191</v>
+      </c>
+      <c r="D724">
+        <v>1</v>
+      </c>
+      <c r="E724">
+        <v>0</v>
+      </c>
+      <c r="F724">
+        <v>1</v>
+      </c>
+      <c r="G724" t="s">
+        <v>205</v>
+      </c>
+      <c r="H724" t="s">
+        <v>207</v>
+      </c>
+      <c r="I724">
+        <v>1</v>
+      </c>
+      <c r="J724" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="725" spans="1:10">
+      <c r="A725" t="s">
+        <v>35</v>
+      </c>
+      <c r="B725" t="s">
+        <v>49</v>
+      </c>
+      <c r="C725" t="s">
+        <v>191</v>
+      </c>
+      <c r="D725">
+        <v>0</v>
+      </c>
+      <c r="E725">
+        <v>1</v>
+      </c>
+      <c r="F725">
+        <v>-1</v>
+      </c>
+      <c r="G725" t="s">
+        <v>205</v>
+      </c>
+      <c r="H725" t="s">
+        <v>206</v>
+      </c>
+      <c r="I725">
+        <v>0</v>
+      </c>
+      <c r="J725" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="726" spans="1:10">
+      <c r="A726" t="s">
+        <v>30</v>
+      </c>
+      <c r="B726" t="s">
+        <v>4</v>
+      </c>
+      <c r="C726" t="s">
+        <v>192</v>
+      </c>
+      <c r="D726">
+        <v>2</v>
+      </c>
+      <c r="E726">
+        <v>1</v>
+      </c>
+      <c r="F726">
+        <v>1</v>
+      </c>
+      <c r="G726" t="s">
+        <v>205</v>
+      </c>
+      <c r="H726" t="s">
+        <v>207</v>
+      </c>
+      <c r="I726">
+        <v>0</v>
+      </c>
+      <c r="J726" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="727" spans="1:10">
+      <c r="A727" t="s">
+        <v>4</v>
+      </c>
+      <c r="B727" t="s">
+        <v>30</v>
+      </c>
+      <c r="C727" t="s">
+        <v>193</v>
+      </c>
+      <c r="D727">
+        <v>1</v>
+      </c>
+      <c r="E727">
+        <v>2</v>
+      </c>
+      <c r="F727">
+        <v>-1</v>
+      </c>
+      <c r="G727" t="s">
+        <v>205</v>
+      </c>
+      <c r="H727" t="s">
+        <v>206</v>
+      </c>
+      <c r="I727">
+        <v>0</v>
+      </c>
+      <c r="J727" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="728" spans="1:10">
+      <c r="A728" t="s">
+        <v>81</v>
+      </c>
+      <c r="B728" t="s">
+        <v>34</v>
+      </c>
+      <c r="C728" t="s">
+        <v>191</v>
+      </c>
+      <c r="D728">
+        <v>3</v>
+      </c>
+      <c r="E728">
+        <v>1</v>
+      </c>
+      <c r="F728">
+        <v>2</v>
+      </c>
+      <c r="G728" t="s">
+        <v>205</v>
+      </c>
+      <c r="H728" t="s">
+        <v>207</v>
+      </c>
+      <c r="I728">
+        <v>0</v>
+      </c>
+      <c r="J728" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="729" spans="1:10">
+      <c r="A729" t="s">
+        <v>34</v>
+      </c>
+      <c r="B729" t="s">
+        <v>81</v>
+      </c>
+      <c r="C729" t="s">
+        <v>191</v>
+      </c>
+      <c r="D729">
+        <v>1</v>
+      </c>
+      <c r="E729">
+        <v>3</v>
+      </c>
+      <c r="F729">
+        <v>-2</v>
+      </c>
+      <c r="G729" t="s">
+        <v>205</v>
+      </c>
+      <c r="H729" t="s">
+        <v>206</v>
+      </c>
+      <c r="I729">
+        <v>0</v>
+      </c>
+      <c r="J729" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="730" spans="1:10">
+      <c r="A730" t="s">
+        <v>11</v>
+      </c>
+      <c r="B730" t="s">
+        <v>28</v>
+      </c>
+      <c r="C730" t="s">
+        <v>191</v>
+      </c>
+      <c r="D730">
+        <v>3</v>
+      </c>
+      <c r="E730">
+        <v>0</v>
+      </c>
+      <c r="F730">
+        <v>3</v>
+      </c>
+      <c r="G730" t="s">
+        <v>205</v>
+      </c>
+      <c r="H730" t="s">
+        <v>207</v>
+      </c>
+      <c r="I730">
+        <v>1</v>
+      </c>
+      <c r="J730" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="731" spans="1:10">
+      <c r="A731" t="s">
+        <v>28</v>
+      </c>
+      <c r="B731" t="s">
+        <v>11</v>
+      </c>
+      <c r="C731" t="s">
+        <v>191</v>
+      </c>
+      <c r="D731">
+        <v>0</v>
+      </c>
+      <c r="E731">
+        <v>3</v>
+      </c>
+      <c r="F731">
+        <v>-3</v>
+      </c>
+      <c r="G731" t="s">
+        <v>205</v>
+      </c>
+      <c r="H731" t="s">
+        <v>206</v>
+      </c>
+      <c r="I731">
+        <v>0</v>
+      </c>
+      <c r="J731" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="732" spans="1:10">
+      <c r="A732" t="s">
+        <v>46</v>
+      </c>
+      <c r="B732" t="s">
+        <v>8</v>
+      </c>
+      <c r="C732" t="s">
+        <v>191</v>
+      </c>
+      <c r="D732">
+        <v>4</v>
+      </c>
+      <c r="E732">
+        <v>2</v>
+      </c>
+      <c r="F732">
+        <v>2</v>
+      </c>
+      <c r="G732" t="s">
+        <v>205</v>
+      </c>
+      <c r="H732" t="s">
+        <v>207</v>
+      </c>
+      <c r="I732">
+        <v>0</v>
+      </c>
+      <c r="J732" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="733" spans="1:10">
+      <c r="A733" t="s">
+        <v>8</v>
+      </c>
+      <c r="B733" t="s">
+        <v>46</v>
+      </c>
+      <c r="C733" t="s">
+        <v>191</v>
+      </c>
+      <c r="D733">
+        <v>2</v>
+      </c>
+      <c r="E733">
+        <v>4</v>
+      </c>
+      <c r="F733">
+        <v>-2</v>
+      </c>
+      <c r="G733" t="s">
+        <v>205</v>
+      </c>
+      <c r="H733" t="s">
+        <v>206</v>
+      </c>
+      <c r="I733">
+        <v>0</v>
+      </c>
+      <c r="J733" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="734" spans="1:10">
+      <c r="A734" t="s">
+        <v>31</v>
+      </c>
+      <c r="B734" t="s">
+        <v>5</v>
+      </c>
+      <c r="C734" t="s">
+        <v>192</v>
+      </c>
+      <c r="D734">
+        <v>3</v>
+      </c>
+      <c r="E734">
+        <v>2</v>
+      </c>
+      <c r="F734">
+        <v>1</v>
+      </c>
+      <c r="G734" t="s">
+        <v>205</v>
+      </c>
+      <c r="H734" t="s">
+        <v>207</v>
+      </c>
+      <c r="I734">
+        <v>0</v>
+      </c>
+      <c r="J734" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="735" spans="1:10">
+      <c r="A735" t="s">
+        <v>5</v>
+      </c>
+      <c r="B735" t="s">
+        <v>31</v>
+      </c>
+      <c r="C735" t="s">
+        <v>193</v>
+      </c>
+      <c r="D735">
+        <v>2</v>
+      </c>
+      <c r="E735">
+        <v>3</v>
+      </c>
+      <c r="F735">
+        <v>-1</v>
+      </c>
+      <c r="G735" t="s">
+        <v>205</v>
+      </c>
+      <c r="H735" t="s">
+        <v>206</v>
+      </c>
+      <c r="I735">
+        <v>0</v>
+      </c>
+      <c r="J735" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="736" spans="1:10">
+      <c r="A736" t="s">
+        <v>14</v>
+      </c>
+      <c r="B736" t="s">
+        <v>33</v>
+      </c>
+      <c r="C736" t="s">
+        <v>191</v>
+      </c>
+      <c r="D736">
+        <v>0</v>
+      </c>
+      <c r="E736">
+        <v>0</v>
+      </c>
+      <c r="F736">
+        <v>0</v>
+      </c>
+      <c r="G736" t="s">
+        <v>205</v>
+      </c>
+      <c r="H736" t="s">
+        <v>208</v>
+      </c>
+      <c r="I736">
+        <v>1</v>
+      </c>
+      <c r="J736" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="737" spans="1:10">
+      <c r="A737" t="s">
+        <v>33</v>
+      </c>
+      <c r="B737" t="s">
+        <v>14</v>
+      </c>
+      <c r="C737" t="s">
+        <v>191</v>
+      </c>
+      <c r="D737">
+        <v>0</v>
+      </c>
+      <c r="E737">
+        <v>0</v>
+      </c>
+      <c r="F737">
+        <v>0</v>
+      </c>
+      <c r="G737" t="s">
+        <v>205</v>
+      </c>
+      <c r="H737" t="s">
+        <v>208</v>
+      </c>
+      <c r="I737">
+        <v>1</v>
+      </c>
+      <c r="J737" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="738" spans="1:10">
+      <c r="A738" t="s">
+        <v>13</v>
+      </c>
+      <c r="B738" t="s">
+        <v>16</v>
+      </c>
+      <c r="C738" t="s">
+        <v>191</v>
+      </c>
+      <c r="D738">
+        <v>2</v>
+      </c>
+      <c r="E738">
+        <v>1</v>
+      </c>
+      <c r="F738">
+        <v>1</v>
+      </c>
+      <c r="G738" t="s">
+        <v>205</v>
+      </c>
+      <c r="H738" t="s">
+        <v>207</v>
+      </c>
+      <c r="I738">
+        <v>0</v>
+      </c>
+      <c r="J738" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="739" spans="1:10">
+      <c r="A739" t="s">
+        <v>16</v>
+      </c>
+      <c r="B739" t="s">
+        <v>13</v>
+      </c>
+      <c r="C739" t="s">
+        <v>191</v>
+      </c>
+      <c r="D739">
+        <v>1</v>
+      </c>
+      <c r="E739">
+        <v>2</v>
+      </c>
+      <c r="F739">
+        <v>-1</v>
+      </c>
+      <c r="G739" t="s">
+        <v>205</v>
+      </c>
+      <c r="H739" t="s">
+        <v>206</v>
+      </c>
+      <c r="I739">
+        <v>0</v>
+      </c>
+      <c r="J739" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="740" spans="1:10">
+      <c r="A740" t="s">
+        <v>7</v>
+      </c>
+      <c r="B740" t="s">
+        <v>43</v>
+      </c>
+      <c r="C740" t="s">
+        <v>191</v>
+      </c>
+      <c r="D740">
+        <v>0</v>
+      </c>
+      <c r="E740">
+        <v>2</v>
+      </c>
+      <c r="F740">
+        <v>-2</v>
+      </c>
+      <c r="G740" t="s">
+        <v>205</v>
+      </c>
+      <c r="H740" t="s">
+        <v>206</v>
+      </c>
+      <c r="I740">
+        <v>0</v>
+      </c>
+      <c r="J740" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="741" spans="1:10">
+      <c r="A741" t="s">
+        <v>43</v>
+      </c>
+      <c r="B741" t="s">
+        <v>7</v>
+      </c>
+      <c r="C741" t="s">
+        <v>191</v>
+      </c>
+      <c r="D741">
+        <v>2</v>
+      </c>
+      <c r="E741">
+        <v>0</v>
+      </c>
+      <c r="F741">
+        <v>2</v>
+      </c>
+      <c r="G741" t="s">
+        <v>205</v>
+      </c>
+      <c r="H741" t="s">
+        <v>207</v>
+      </c>
+      <c r="I741">
+        <v>1</v>
+      </c>
+      <c r="J741" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="742" spans="1:10">
+      <c r="A742" t="s">
+        <v>38</v>
+      </c>
+      <c r="B742" t="s">
+        <v>29</v>
+      </c>
+      <c r="C742" t="s">
+        <v>191</v>
+      </c>
+      <c r="D742">
+        <v>1</v>
+      </c>
+      <c r="E742">
+        <v>1</v>
+      </c>
+      <c r="F742">
+        <v>0</v>
+      </c>
+      <c r="G742" t="s">
+        <v>205</v>
+      </c>
+      <c r="H742" t="s">
+        <v>208</v>
+      </c>
+      <c r="I742">
+        <v>0</v>
+      </c>
+      <c r="J742" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="743" spans="1:10">
+      <c r="A743" t="s">
+        <v>29</v>
+      </c>
+      <c r="B743" t="s">
+        <v>38</v>
+      </c>
+      <c r="C743" t="s">
+        <v>191</v>
+      </c>
+      <c r="D743">
+        <v>1</v>
+      </c>
+      <c r="E743">
+        <v>1</v>
+      </c>
+      <c r="F743">
+        <v>0</v>
+      </c>
+      <c r="G743" t="s">
+        <v>205</v>
+      </c>
+      <c r="H743" t="s">
+        <v>208</v>
+      </c>
+      <c r="I743">
+        <v>0</v>
+      </c>
+      <c r="J743" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="744" spans="1:10">
+      <c r="A744" t="s">
+        <v>50</v>
+      </c>
+      <c r="B744" t="s">
+        <v>25</v>
+      </c>
+      <c r="C744" t="s">
+        <v>191</v>
+      </c>
+      <c r="D744">
+        <v>1</v>
+      </c>
+      <c r="E744">
+        <v>3</v>
+      </c>
+      <c r="F744">
+        <v>-2</v>
+      </c>
+      <c r="G744" t="s">
+        <v>205</v>
+      </c>
+      <c r="H744" t="s">
+        <v>206</v>
+      </c>
+      <c r="I744">
+        <v>0</v>
+      </c>
+      <c r="J744" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="745" spans="1:10">
+      <c r="A745" t="s">
+        <v>25</v>
+      </c>
+      <c r="B745" t="s">
+        <v>50</v>
+      </c>
+      <c r="C745" t="s">
+        <v>191</v>
+      </c>
+      <c r="D745">
+        <v>3</v>
+      </c>
+      <c r="E745">
+        <v>1</v>
+      </c>
+      <c r="F745">
+        <v>2</v>
+      </c>
+      <c r="G745" t="s">
+        <v>205</v>
+      </c>
+      <c r="H745" t="s">
+        <v>207</v>
+      </c>
+      <c r="I745">
+        <v>0</v>
+      </c>
+      <c r="J745" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10">
+      <c r="A746" t="s">
+        <v>44</v>
+      </c>
+      <c r="B746" t="s">
+        <v>37</v>
+      </c>
+      <c r="C746" t="s">
+        <v>191</v>
+      </c>
+      <c r="D746">
+        <v>1</v>
+      </c>
+      <c r="E746">
+        <v>1</v>
+      </c>
+      <c r="F746">
+        <v>0</v>
+      </c>
+      <c r="G746" t="s">
+        <v>205</v>
+      </c>
+      <c r="H746" t="s">
+        <v>208</v>
+      </c>
+      <c r="I746">
+        <v>0</v>
+      </c>
+      <c r="J746" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10">
+      <c r="A747" t="s">
+        <v>37</v>
+      </c>
+      <c r="B747" t="s">
+        <v>44</v>
+      </c>
+      <c r="C747" t="s">
+        <v>191</v>
+      </c>
+      <c r="D747">
+        <v>1</v>
+      </c>
+      <c r="E747">
+        <v>1</v>
+      </c>
+      <c r="F747">
+        <v>0</v>
+      </c>
+      <c r="G747" t="s">
+        <v>205</v>
+      </c>
+      <c r="H747" t="s">
+        <v>208</v>
+      </c>
+      <c r="I747">
+        <v>0</v>
+      </c>
+      <c r="J747" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10">
+      <c r="A748" t="s">
+        <v>18</v>
+      </c>
+      <c r="B748" t="s">
+        <v>51</v>
+      </c>
+      <c r="C748" t="s">
+        <v>191</v>
+      </c>
+      <c r="D748">
+        <v>5</v>
+      </c>
+      <c r="E748">
+        <v>1</v>
+      </c>
+      <c r="F748">
+        <v>4</v>
+      </c>
+      <c r="G748" t="s">
+        <v>205</v>
+      </c>
+      <c r="H748" t="s">
+        <v>207</v>
+      </c>
+      <c r="I748">
+        <v>0</v>
+      </c>
+      <c r="J748" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10">
+      <c r="A749" t="s">
+        <v>51</v>
+      </c>
+      <c r="B749" t="s">
+        <v>18</v>
+      </c>
+      <c r="C749" t="s">
+        <v>191</v>
+      </c>
+      <c r="D749">
+        <v>1</v>
+      </c>
+      <c r="E749">
+        <v>5</v>
+      </c>
+      <c r="F749">
+        <v>-4</v>
+      </c>
+      <c r="G749" t="s">
+        <v>205</v>
+      </c>
+      <c r="H749" t="s">
+        <v>206</v>
+      </c>
+      <c r="I749">
+        <v>0</v>
+      </c>
+      <c r="J749" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10">
+      <c r="A750" t="s">
+        <v>42</v>
+      </c>
+      <c r="B750" t="s">
+        <v>32</v>
+      </c>
+      <c r="C750" t="s">
+        <v>191</v>
+      </c>
+      <c r="D750">
+        <v>0</v>
+      </c>
+      <c r="E750">
+        <v>0</v>
+      </c>
+      <c r="F750">
+        <v>0</v>
+      </c>
+      <c r="G750" t="s">
+        <v>205</v>
+      </c>
+      <c r="H750" t="s">
+        <v>208</v>
+      </c>
+      <c r="I750">
+        <v>1</v>
+      </c>
+      <c r="J750" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10">
+      <c r="A751" t="s">
+        <v>32</v>
+      </c>
+      <c r="B751" t="s">
+        <v>42</v>
+      </c>
+      <c r="C751" t="s">
+        <v>191</v>
+      </c>
+      <c r="D751">
+        <v>0</v>
+      </c>
+      <c r="E751">
+        <v>0</v>
+      </c>
+      <c r="F751">
+        <v>0</v>
+      </c>
+      <c r="G751" t="s">
+        <v>205</v>
+      </c>
+      <c r="H751" t="s">
+        <v>208</v>
+      </c>
+      <c r="I751">
+        <v>1</v>
+      </c>
+      <c r="J751" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10">
+      <c r="A752" t="s">
+        <v>15</v>
+      </c>
+      <c r="B752" t="s">
+        <v>21</v>
+      </c>
+      <c r="C752" t="s">
+        <v>191</v>
+      </c>
+      <c r="D752">
+        <v>0</v>
+      </c>
+      <c r="E752">
+        <v>1</v>
+      </c>
+      <c r="F752">
+        <v>-1</v>
+      </c>
+      <c r="G752" t="s">
+        <v>205</v>
+      </c>
+      <c r="H752" t="s">
+        <v>206</v>
+      </c>
+      <c r="I752">
+        <v>0</v>
+      </c>
+      <c r="J752" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="753" spans="1:10">
+      <c r="A753" t="s">
+        <v>21</v>
+      </c>
+      <c r="B753" t="s">
+        <v>15</v>
+      </c>
+      <c r="C753" t="s">
+        <v>191</v>
+      </c>
+      <c r="D753">
+        <v>1</v>
+      </c>
+      <c r="E753">
+        <v>0</v>
+      </c>
+      <c r="F753">
+        <v>1</v>
+      </c>
+      <c r="G753" t="s">
+        <v>205</v>
+      </c>
+      <c r="H753" t="s">
+        <v>207</v>
+      </c>
+      <c r="I753">
+        <v>1</v>
+      </c>
+      <c r="J753" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="754" spans="1:10">
+      <c r="A754" t="s">
+        <v>22</v>
+      </c>
+      <c r="B754" t="s">
+        <v>24</v>
+      </c>
+      <c r="C754" t="s">
+        <v>191</v>
+      </c>
+      <c r="D754">
+        <v>4</v>
+      </c>
+      <c r="E754">
+        <v>1</v>
+      </c>
+      <c r="F754">
+        <v>3</v>
+      </c>
+      <c r="G754" t="s">
+        <v>205</v>
+      </c>
+      <c r="H754" t="s">
+        <v>207</v>
+      </c>
+      <c r="I754">
+        <v>0</v>
+      </c>
+      <c r="J754" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="755" spans="1:10">
+      <c r="A755" t="s">
+        <v>24</v>
+      </c>
+      <c r="B755" t="s">
+        <v>22</v>
+      </c>
+      <c r="C755" t="s">
+        <v>191</v>
+      </c>
+      <c r="D755">
+        <v>1</v>
+      </c>
+      <c r="E755">
+        <v>4</v>
+      </c>
+      <c r="F755">
+        <v>-3</v>
+      </c>
+      <c r="G755" t="s">
+        <v>205</v>
+      </c>
+      <c r="H755" t="s">
+        <v>206</v>
+      </c>
+      <c r="I755">
+        <v>0</v>
+      </c>
+      <c r="J755" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="756" spans="1:10">
+      <c r="A756" t="s">
+        <v>48</v>
+      </c>
+      <c r="B756" t="s">
+        <v>36</v>
+      </c>
+      <c r="C756" t="s">
+        <v>191</v>
+      </c>
+      <c r="D756">
+        <v>5</v>
+      </c>
+      <c r="E756">
+        <v>0</v>
+      </c>
+      <c r="F756">
+        <v>5</v>
+      </c>
+      <c r="G756" t="s">
+        <v>205</v>
+      </c>
+      <c r="H756" t="s">
+        <v>207</v>
+      </c>
+      <c r="I756">
+        <v>1</v>
+      </c>
+      <c r="J756" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="757" spans="1:10">
+      <c r="A757" t="s">
+        <v>36</v>
+      </c>
+      <c r="B757" t="s">
+        <v>48</v>
+      </c>
+      <c r="C757" t="s">
+        <v>191</v>
+      </c>
+      <c r="D757">
+        <v>0</v>
+      </c>
+      <c r="E757">
+        <v>5</v>
+      </c>
+      <c r="F757">
+        <v>-5</v>
+      </c>
+      <c r="G757" t="s">
+        <v>205</v>
+      </c>
+      <c r="H757" t="s">
+        <v>206</v>
+      </c>
+      <c r="I757">
+        <v>0</v>
+      </c>
+      <c r="J757" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="758" spans="1:10">
+      <c r="A758" t="s">
+        <v>10</v>
+      </c>
+      <c r="B758" t="s">
+        <v>39</v>
+      </c>
+      <c r="C758" t="s">
+        <v>191</v>
+      </c>
+      <c r="D758">
+        <v>3</v>
+      </c>
+      <c r="E758">
+        <v>1</v>
+      </c>
+      <c r="F758">
+        <v>2</v>
+      </c>
+      <c r="G758" t="s">
+        <v>205</v>
+      </c>
+      <c r="H758" t="s">
+        <v>207</v>
+      </c>
+      <c r="I758">
+        <v>0</v>
+      </c>
+      <c r="J758" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="759" spans="1:10">
+      <c r="A759" t="s">
+        <v>39</v>
+      </c>
+      <c r="B759" t="s">
+        <v>10</v>
+      </c>
+      <c r="C759" t="s">
+        <v>191</v>
+      </c>
+      <c r="D759">
+        <v>1</v>
+      </c>
+      <c r="E759">
+        <v>3</v>
+      </c>
+      <c r="F759">
+        <v>-2</v>
+      </c>
+      <c r="G759" t="s">
+        <v>205</v>
+      </c>
+      <c r="H759" t="s">
+        <v>206</v>
+      </c>
+      <c r="I759">
+        <v>0</v>
+      </c>
+      <c r="J759" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="760" spans="1:10">
+      <c r="A760" t="s">
+        <v>17</v>
+      </c>
+      <c r="B760" t="s">
+        <v>41</v>
+      </c>
+      <c r="C760" t="s">
+        <v>191</v>
+      </c>
+      <c r="D760">
+        <v>3</v>
+      </c>
+      <c r="E760">
+        <v>3</v>
+      </c>
+      <c r="F760">
+        <v>0</v>
+      </c>
+      <c r="G760" t="s">
+        <v>205</v>
+      </c>
+      <c r="H760" t="s">
+        <v>208</v>
+      </c>
+      <c r="I760">
+        <v>0</v>
+      </c>
+      <c r="J760" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="761" spans="1:10">
+      <c r="A761" t="s">
+        <v>41</v>
+      </c>
+      <c r="B761" t="s">
+        <v>17</v>
+      </c>
+      <c r="C761" t="s">
+        <v>191</v>
+      </c>
+      <c r="D761">
+        <v>3</v>
+      </c>
+      <c r="E761">
+        <v>3</v>
+      </c>
+      <c r="F761">
+        <v>0</v>
+      </c>
+      <c r="G761" t="s">
+        <v>205</v>
+      </c>
+      <c r="H761" t="s">
+        <v>208</v>
+      </c>
+      <c r="I761">
+        <v>0</v>
+      </c>
+      <c r="J761" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="762" spans="1:10">
+      <c r="A762" t="s">
+        <v>12</v>
+      </c>
+      <c r="B762" t="s">
+        <v>26</v>
+      </c>
+      <c r="C762" t="s">
+        <v>191</v>
+      </c>
+      <c r="D762">
+        <v>0</v>
+      </c>
+      <c r="E762">
+        <v>0</v>
+      </c>
+      <c r="F762">
+        <v>0</v>
+      </c>
+      <c r="G762" t="s">
+        <v>205</v>
+      </c>
+      <c r="H762" t="s">
+        <v>208</v>
+      </c>
+      <c r="I762">
+        <v>1</v>
+      </c>
+      <c r="J762" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="763" spans="1:10">
+      <c r="A763" t="s">
+        <v>26</v>
+      </c>
+      <c r="B763" t="s">
+        <v>12</v>
+      </c>
+      <c r="C763" t="s">
+        <v>191</v>
+      </c>
+      <c r="D763">
+        <v>0</v>
+      </c>
+      <c r="E763">
+        <v>0</v>
+      </c>
+      <c r="F763">
+        <v>0</v>
+      </c>
+      <c r="G763" t="s">
+        <v>205</v>
+      </c>
+      <c r="H763" t="s">
+        <v>208</v>
+      </c>
+      <c r="I763">
+        <v>1</v>
+      </c>
+      <c r="J763" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="764" spans="1:10">
+      <c r="A764" t="s">
+        <v>47</v>
+      </c>
+      <c r="B764" t="s">
+        <v>40</v>
+      </c>
+      <c r="C764" t="s">
+        <v>191</v>
+      </c>
+      <c r="D764">
+        <v>3</v>
+      </c>
+      <c r="E764">
+        <v>1</v>
+      </c>
+      <c r="F764">
+        <v>2</v>
+      </c>
+      <c r="G764" t="s">
+        <v>205</v>
+      </c>
+      <c r="H764" t="s">
+        <v>207</v>
+      </c>
+      <c r="I764">
+        <v>0</v>
+      </c>
+      <c r="J764" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="765" spans="1:10">
+      <c r="A765" t="s">
+        <v>40</v>
+      </c>
+      <c r="B765" t="s">
+        <v>47</v>
+      </c>
+      <c r="C765" t="s">
+        <v>191</v>
+      </c>
+      <c r="D765">
+        <v>1</v>
+      </c>
+      <c r="E765">
+        <v>3</v>
+      </c>
+      <c r="F765">
+        <v>-2</v>
+      </c>
+      <c r="G765" t="s">
+        <v>205</v>
+      </c>
+      <c r="H765" t="s">
+        <v>206</v>
+      </c>
+      <c r="I765">
+        <v>0</v>
+      </c>
+      <c r="J765" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="766" spans="1:10">
+      <c r="A766" t="s">
+        <v>23</v>
+      </c>
+      <c r="B766" t="s">
+        <v>9</v>
+      </c>
+      <c r="C766" t="s">
+        <v>191</v>
+      </c>
+      <c r="D766">
+        <v>2</v>
+      </c>
+      <c r="E766">
+        <v>0</v>
+      </c>
+      <c r="F766">
+        <v>2</v>
+      </c>
+      <c r="G766" t="s">
+        <v>205</v>
+      </c>
+      <c r="H766" t="s">
+        <v>207</v>
+      </c>
+      <c r="I766">
+        <v>1</v>
+      </c>
+      <c r="J766" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="767" spans="1:10">
+      <c r="A767" t="s">
+        <v>9</v>
+      </c>
+      <c r="B767" t="s">
+        <v>23</v>
+      </c>
+      <c r="C767" t="s">
+        <v>191</v>
+      </c>
+      <c r="D767">
+        <v>0</v>
+      </c>
+      <c r="E767">
+        <v>2</v>
+      </c>
+      <c r="F767">
+        <v>-2</v>
+      </c>
+      <c r="G767" t="s">
+        <v>205</v>
+      </c>
+      <c r="H767" t="s">
+        <v>206</v>
+      </c>
+      <c r="I767">
+        <v>0</v>
+      </c>
+      <c r="J767" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="768" spans="1:10">
+      <c r="A768" t="s">
+        <v>20</v>
+      </c>
+      <c r="B768" t="s">
+        <v>45</v>
+      </c>
+      <c r="C768" t="s">
+        <v>191</v>
+      </c>
+      <c r="D768">
+        <v>2</v>
+      </c>
+      <c r="E768">
+        <v>1</v>
+      </c>
+      <c r="F768">
+        <v>1</v>
+      </c>
+      <c r="G768" t="s">
+        <v>205</v>
+      </c>
+      <c r="H768" t="s">
+        <v>207</v>
+      </c>
+      <c r="I768">
+        <v>0</v>
+      </c>
+      <c r="J768" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="769" spans="1:10">
+      <c r="A769" t="s">
+        <v>45</v>
+      </c>
+      <c r="B769" t="s">
+        <v>20</v>
+      </c>
+      <c r="C769" t="s">
+        <v>191</v>
+      </c>
+      <c r="D769">
+        <v>1</v>
+      </c>
+      <c r="E769">
+        <v>2</v>
+      </c>
+      <c r="F769">
+        <v>-1</v>
+      </c>
+      <c r="G769" t="s">
+        <v>205</v>
+      </c>
+      <c r="H769" t="s">
+        <v>206</v>
+      </c>
+      <c r="I769">
+        <v>0</v>
+      </c>
+      <c r="J769" s="1">
+        <v>46200</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J673" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>